--- a/tiflow-chargeitem/develop/2.0.0-ballot.2/StructureDefinition-GEM-ERPCHRG-PR-Consent.xlsx
+++ b/tiflow-chargeitem/develop/2.0.0-ballot.2/StructureDefinition-GEM-ERPCHRG-PR-Consent.xlsx
@@ -16,7 +16,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3230" uniqueCount="506">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3241" uniqueCount="523">
   <si>
     <t>Property</t>
   </si>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2028-04-01</t>
+    <t>2026-06-30</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -269,7 +269,7 @@
   </si>
   <si>
     <t>dom-2:If the resource is contained in another resource, it SHALL NOT contain nested Resources {contained.contained.empty()}
-dom-3:If the resource is contained in another resource, it SHALL be referred to from elsewhere in the resource or SHALL refer to the containing resource {contained.where((('#'+id in (%resource.descendants().reference | %resource.descendants().as(canonical) | %resource.descendants().as(uri) | %resource.descendants().as(url))) or descendants().where(reference = '#').exists() or descendants().where(as(canonical) = '#').exists() or descendants().where(as(canonical) = '#').exists()).not()).trace('unmatched', id).empty()}dom-4:If a resource is contained in another resource, it SHALL NOT have a meta.versionId or a meta.lastUpdated {contained.meta.versionId.empty() and contained.meta.lastUpdated.empty()}dom-5:If a resource is contained in another resource, it SHALL NOT have a security label {contained.meta.security.empty()}dom-6:A resource should have narrative for robust management {text.`div`.exists()}ppc-1:Either a Policy or PolicyRule {policy.exists() or policyRule.exists()}ppc-2:IF Scope=privacy, there must be a patient {patient.exists() or scope.coding.where(system='something' and code='patient-privacy').exists().not()}ppc-3:IF Scope=research, there must be a patient {patient.exists() or scope.coding.where(system='something' and code='research').exists().not()}ppc-4:IF Scope=adr, there must be a patient {patient.exists() or scope.coding.where(system='something' and code='adr').exists().not()}ppc-5:IF Scope=treatment, there must be a patient {patient.exists() or scope.coding.where(system='something' and code='treatment').exists().not()}</t>
+dom-3:If the resource is contained in another resource, it SHALL be referred to from elsewhere in the resource or SHALL refer to the containing resource {contained.where((('#'+id in (%resource.descendants().reference | %resource.descendants().as(canonical) | %resource.descendants().as(uri) | %resource.descendants().as(url))) or descendants().where(reference = '#').exists() or descendants().where(as(canonical) = '#').exists() or descendants().where(as(canonical) = '#').exists()).not()).trace('unmatched', id).empty()}dom-4:If a resource is contained in another resource, it SHALL NOT have a meta.versionId or a meta.lastUpdated {contained.meta.versionId.empty() and contained.meta.lastUpdated.empty()}dom-5:If a resource is contained in another resource, it SHALL NOT have a security label {contained.meta.security.empty()}dom-6:A resource should have narrative for robust management {text.`div`.exists()}ppc-4:IF Scope=adr, there must be a patient {patient.exists() or scope.coding.where(system='something' and code='adr').exists().not()}ppc-5:IF Scope=treatment, there must be a patient {patient.exists() or scope.coding.where(system='something' and code='treatment').exists().not()}ppc-2:IF Scope=privacy, there must be a patient {patient.exists() or scope.coding.where(system='something' and code='patient-privacy').exists().not()}ppc-3:IF Scope=research, there must be a patient {patient.exists() or scope.coding.where(system='something' and code='research').exists().not()}ppc-1:Either a Policy or PolicyRule {policy.exists() or policyRule.exists()}</t>
   </si>
   <si>
     <t>Event</t>
@@ -443,6 +443,16 @@
   </si>
   <si>
     <t>There can be no stigma associated with the use of extensions by any application, project, or standard - regardless of the institution or jurisdiction that uses or defines the extensions.  The use of extensions is what allows the FHIR specification to retain a core level of simplicity for everyone.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">value:url}
+</t>
+  </si>
+  <si>
+    <t>Extensions are always sliced by (at least) url</t>
+  </si>
+  <si>
+    <t>open</t>
   </si>
   <si>
     <t>DomainResource.extension</t>
@@ -490,7 +500,14 @@
 &lt;/valueIdentifier&gt;</t>
   </si>
   <si>
+    <t xml:space="preserve">ele-1
+</t>
+  </si>
+  <si>
     <t>Event.identifier</t>
+  </si>
+  <si>
+    <t>CX / EI (occasionally, more often EI maps to a resource id or a URL)</t>
   </si>
   <si>
     <t>.id</t>
@@ -548,6 +565,9 @@
     <t>A selector of the type of consent being presented: ADR, Privacy, Treatment, Research.  This list is now extensible.</t>
   </si>
   <si>
+    <t>Not all terminology uses fit this general pattern. In some cases, models should not use CodeableConcept and use Coding directly and provide their own structure for managing text, codings, translations and the relationship between elements and pre- and post-coordination.</t>
+  </si>
+  <si>
     <t>extensible</t>
   </si>
   <si>
@@ -555,6 +575,12 @@
   </si>
   <si>
     <t>http://hl7.org/fhir/ValueSet/consent-scope|4.0.1</t>
+  </si>
+  <si>
+    <t>CE/CNE/CWE</t>
+  </si>
+  <si>
+    <t>CD</t>
   </si>
   <si>
     <t>Consent.scope.id</t>
@@ -582,16 +608,6 @@
     <t>May be used to represent additional information that is not part of the basic definition of the element. To make the use of extensions safe and manageable, there is a strict set of governance  applied to the definition and use of extensions. Though any implementer can define an extension, there is a set of requirements that SHALL be met as part of the definition of the extension.</t>
   </si>
   <si>
-    <t xml:space="preserve">value:url}
-</t>
-  </si>
-  <si>
-    <t>Extensions are always sliced by (at least) url</t>
-  </si>
-  <si>
-    <t>open</t>
-  </si>
-  <si>
     <t>Element.extension</t>
   </si>
   <si>
@@ -710,6 +726,9 @@
     <t>A representation of the meaning of the code in the system, following the rules of the system.</t>
   </si>
   <si>
+    <t>Note that FHIR strings SHALL NOT exceed 1MB in size</t>
+  </si>
+  <si>
     <t>Need to be able to carry a human-readable meaning of the code for readers that do not know  the system.</t>
   </si>
   <si>
@@ -815,6 +834,10 @@
   </si>
   <si>
     <t>Commonly, the patient the consent pertains to is the author, but for young and old people, it may be some other person.</t>
+  </si>
+  <si>
+    <t>ele-1:All FHIR elements must have a @value or children {hasValue() or (children().count() &gt; id.count())}
+ref-1:SHALL have a contained resource if a local reference is provided {reference.startsWith('#').not() or (reference.substring(1).trace('url') in %rootResource.contained.id.trace('ids'))}</t>
   </si>
   <si>
     <t>Event.subject</t>
@@ -1041,7 +1064,15 @@
     <t>Time period during which identifier is/was valid for use.</t>
   </si>
   <si>
+    <t>A Period specifies a range of time; the context of use will specify whether the entire range applies (e.g. "the patient was an inpatient of the hospital for this time range") or one value from the range applies (e.g. "give to the patient between these two times").
+Period is not used for a duration (a measure of elapsed time). See [Duration](http://hl7.org/fhir/R4/datatypes.html#Duration).</t>
+  </si>
+  <si>
     <t>Identifier.period</t>
+  </si>
+  <si>
+    <t>ele-1:All FHIR elements must have a @value or children {hasValue() or (children().count() &gt; id.count())}
+per-1:If present, start SHALL have a lower value than end {start.hasValue().not() or end.hasValue().not() or (start &lt;= end)}</t>
   </si>
   <si>
     <t>CX.7 + CX.8</t>
@@ -1166,6 +1197,9 @@
     <t>Field 24/ ConsenterID</t>
   </si>
   <si>
+    <t>The target of a resource reference is a RIM entry point (Act, Role, or Entity)</t>
+  </si>
+  <si>
     <t>FiveWs.actor</t>
   </si>
   <si>
@@ -1186,6 +1220,9 @@
     <t>The organization that manages the consent, and the framework within which it is executed.</t>
   </si>
   <si>
+    <t>References SHALL be a reference to an actual FHIR resource, and SHALL be resolveable (allowing for access control, temporary unavailability, etc.). Resolution can be either by retrieval from the URL, or, where applicable by resource type, by treating an absolute reference as a canonical URL and looking it up in a local registry/repository.</t>
+  </si>
+  <si>
     <t>FiveWs.witness</t>
   </si>
   <si>
@@ -1253,6 +1290,9 @@
     <t>Entity or Organization having regulatory jurisdiction or accountability for  enforcing policies pertaining to Consent Directives.</t>
   </si>
   <si>
+    <t>see http://en.wikipedia.org/wiki/Uniform_resource_identifier</t>
+  </si>
+  <si>
     <t xml:space="preserve">ppc-1
 </t>
   </si>
@@ -1284,6 +1324,10 @@
     <t>http://terminology.hl7.org/ValueSet/v3-ActCode</t>
   </si>
   <si>
+    <t>ele-1
+ppc-1</t>
+  </si>
+  <si>
     <t>Consent.verification</t>
   </si>
   <si>
@@ -1375,6 +1419,12 @@
     <t>The timeframe in this rule is valid.</t>
   </si>
   <si>
+    <t>DR</t>
+  </si>
+  <si>
+    <t>IVL&lt;TS&gt;[lowClosed="true" and highClosed="true"] or URG&lt;TS&gt;[lowClosed="true" and highClosed="true"]</t>
+  </si>
+  <si>
     <t>Consent.provision.actor</t>
   </si>
   <si>
@@ -1464,6 +1514,12 @@
   </si>
   <si>
     <t>http://hl7.org/fhir/ValueSet/security-labels|4.0.1</t>
+  </si>
+  <si>
+    <t>CE/CNE/CWE subset one of the sets of component 1-3 or 4-6</t>
+  </si>
+  <si>
+    <t>CV</t>
   </si>
   <si>
     <t>Consent.provision.purpose</t>
@@ -1943,7 +1999,7 @@
     <col min="34" max="34" width="9.46484375" customWidth="true" bestFit="true"/>
     <col min="35" max="35" width="100.703125" customWidth="true"/>
     <col min="37" max="37" width="25.4609375" customWidth="true" bestFit="true"/>
-    <col min="38" max="38" width="39.8203125" customWidth="true" bestFit="true"/>
+    <col min="38" max="38" width="53.91015625" customWidth="true" bestFit="true"/>
     <col min="39" max="39" width="87.9765625" customWidth="true" bestFit="true"/>
     <col min="40" max="40" width="31.65234375" customWidth="true" bestFit="true"/>
   </cols>
@@ -2941,19 +2997,19 @@
         <v>76</v>
       </c>
       <c r="AB9" t="s" s="2">
-        <v>76</v>
+        <v>138</v>
       </c>
       <c r="AC9" t="s" s="2">
-        <v>76</v>
+        <v>139</v>
       </c>
       <c r="AD9" t="s" s="2">
         <v>76</v>
       </c>
       <c r="AE9" t="s" s="2">
-        <v>76</v>
+        <v>140</v>
       </c>
       <c r="AF9" t="s" s="2">
-        <v>138</v>
+        <v>141</v>
       </c>
       <c r="AG9" t="s" s="2">
         <v>77</v>
@@ -2965,7 +3021,7 @@
         <v>76</v>
       </c>
       <c r="AJ9" t="s" s="2">
-        <v>139</v>
+        <v>142</v>
       </c>
       <c r="AK9" t="s" s="2">
         <v>76</v>
@@ -2982,10 +3038,10 @@
     </row>
     <row r="10" hidden="true">
       <c r="A10" t="s" s="2">
-        <v>140</v>
+        <v>143</v>
       </c>
       <c r="B10" t="s" s="2">
-        <v>140</v>
+        <v>143</v>
       </c>
       <c r="C10" s="2"/>
       <c r="D10" t="s" s="2">
@@ -3011,16 +3067,16 @@
         <v>134</v>
       </c>
       <c r="L10" t="s" s="2">
-        <v>141</v>
+        <v>144</v>
       </c>
       <c r="M10" t="s" s="2">
-        <v>142</v>
+        <v>145</v>
       </c>
       <c r="N10" t="s" s="2">
         <v>137</v>
       </c>
       <c r="O10" t="s" s="2">
-        <v>143</v>
+        <v>146</v>
       </c>
       <c r="P10" t="s" s="2">
         <v>76</v>
@@ -3057,19 +3113,19 @@
         <v>76</v>
       </c>
       <c r="AB10" t="s" s="2">
-        <v>76</v>
+        <v>138</v>
       </c>
       <c r="AC10" t="s" s="2">
-        <v>76</v>
+        <v>139</v>
       </c>
       <c r="AD10" t="s" s="2">
         <v>76</v>
       </c>
       <c r="AE10" t="s" s="2">
-        <v>76</v>
+        <v>140</v>
       </c>
       <c r="AF10" t="s" s="2">
-        <v>144</v>
+        <v>147</v>
       </c>
       <c r="AG10" t="s" s="2">
         <v>77</v>
@@ -3081,7 +3137,7 @@
         <v>76</v>
       </c>
       <c r="AJ10" t="s" s="2">
-        <v>139</v>
+        <v>142</v>
       </c>
       <c r="AK10" t="s" s="2">
         <v>76</v>
@@ -3098,10 +3154,10 @@
     </row>
     <row r="11" hidden="true">
       <c r="A11" t="s" s="2">
-        <v>145</v>
+        <v>148</v>
       </c>
       <c r="B11" t="s" s="2">
-        <v>145</v>
+        <v>148</v>
       </c>
       <c r="C11" s="2"/>
       <c r="D11" t="s" s="2">
@@ -3124,16 +3180,16 @@
         <v>89</v>
       </c>
       <c r="K11" t="s" s="2">
-        <v>146</v>
+        <v>149</v>
       </c>
       <c r="L11" t="s" s="2">
-        <v>147</v>
+        <v>150</v>
       </c>
       <c r="M11" t="s" s="2">
-        <v>148</v>
+        <v>151</v>
       </c>
       <c r="N11" t="s" s="2">
-        <v>149</v>
+        <v>152</v>
       </c>
       <c r="O11" s="2"/>
       <c r="P11" t="s" s="2">
@@ -3147,7 +3203,7 @@
         <v>76</v>
       </c>
       <c r="T11" t="s" s="2">
-        <v>150</v>
+        <v>153</v>
       </c>
       <c r="U11" t="s" s="2">
         <v>76</v>
@@ -3183,7 +3239,7 @@
         <v>76</v>
       </c>
       <c r="AF11" t="s" s="2">
-        <v>145</v>
+        <v>148</v>
       </c>
       <c r="AG11" t="s" s="2">
         <v>77</v>
@@ -3192,30 +3248,30 @@
         <v>78</v>
       </c>
       <c r="AI11" t="s" s="2">
-        <v>76</v>
+        <v>154</v>
       </c>
       <c r="AJ11" t="s" s="2">
         <v>100</v>
       </c>
       <c r="AK11" t="s" s="2">
-        <v>151</v>
+        <v>155</v>
       </c>
       <c r="AL11" t="s" s="2">
-        <v>76</v>
+        <v>156</v>
       </c>
       <c r="AM11" t="s" s="2">
-        <v>152</v>
+        <v>157</v>
       </c>
       <c r="AN11" t="s" s="2">
-        <v>153</v>
+        <v>158</v>
       </c>
     </row>
     <row r="12" hidden="true">
       <c r="A12" t="s" s="2">
-        <v>154</v>
+        <v>159</v>
       </c>
       <c r="B12" t="s" s="2">
-        <v>154</v>
+        <v>159</v>
       </c>
       <c r="C12" s="2"/>
       <c r="D12" t="s" s="2">
@@ -3241,16 +3297,16 @@
         <v>108</v>
       </c>
       <c r="L12" t="s" s="2">
-        <v>155</v>
+        <v>160</v>
       </c>
       <c r="M12" t="s" s="2">
-        <v>156</v>
+        <v>161</v>
       </c>
       <c r="N12" t="s" s="2">
-        <v>157</v>
+        <v>162</v>
       </c>
       <c r="O12" t="s" s="2">
-        <v>158</v>
+        <v>163</v>
       </c>
       <c r="P12" t="s" s="2">
         <v>76</v>
@@ -3275,31 +3331,31 @@
         <v>76</v>
       </c>
       <c r="X12" t="s" s="2">
+        <v>164</v>
+      </c>
+      <c r="Y12" t="s" s="2">
+        <v>165</v>
+      </c>
+      <c r="Z12" t="s" s="2">
+        <v>166</v>
+      </c>
+      <c r="AA12" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="AB12" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="AC12" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="AD12" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="AE12" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="AF12" t="s" s="2">
         <v>159</v>
-      </c>
-      <c r="Y12" t="s" s="2">
-        <v>160</v>
-      </c>
-      <c r="Z12" t="s" s="2">
-        <v>161</v>
-      </c>
-      <c r="AA12" t="s" s="2">
-        <v>76</v>
-      </c>
-      <c r="AB12" t="s" s="2">
-        <v>76</v>
-      </c>
-      <c r="AC12" t="s" s="2">
-        <v>76</v>
-      </c>
-      <c r="AD12" t="s" s="2">
-        <v>76</v>
-      </c>
-      <c r="AE12" t="s" s="2">
-        <v>76</v>
-      </c>
-      <c r="AF12" t="s" s="2">
-        <v>154</v>
       </c>
       <c r="AG12" t="s" s="2">
         <v>88</v>
@@ -3314,24 +3370,24 @@
         <v>100</v>
       </c>
       <c r="AK12" t="s" s="2">
-        <v>162</v>
+        <v>167</v>
       </c>
       <c r="AL12" t="s" s="2">
-        <v>163</v>
+        <v>168</v>
       </c>
       <c r="AM12" t="s" s="2">
-        <v>164</v>
+        <v>169</v>
       </c>
       <c r="AN12" t="s" s="2">
-        <v>165</v>
+        <v>170</v>
       </c>
     </row>
     <row r="13" hidden="true">
       <c r="A13" t="s" s="2">
-        <v>166</v>
+        <v>171</v>
       </c>
       <c r="B13" t="s" s="2">
-        <v>166</v>
+        <v>171</v>
       </c>
       <c r="C13" s="2"/>
       <c r="D13" t="s" s="2">
@@ -3354,15 +3410,17 @@
         <v>89</v>
       </c>
       <c r="K13" t="s" s="2">
-        <v>167</v>
+        <v>172</v>
       </c>
       <c r="L13" t="s" s="2">
-        <v>168</v>
+        <v>173</v>
       </c>
       <c r="M13" t="s" s="2">
-        <v>169</v>
-      </c>
-      <c r="N13" s="2"/>
+        <v>174</v>
+      </c>
+      <c r="N13" t="s" s="2">
+        <v>175</v>
+      </c>
       <c r="O13" s="2"/>
       <c r="P13" t="s" s="2">
         <v>76</v>
@@ -3387,32 +3445,32 @@
         <v>76</v>
       </c>
       <c r="X13" t="s" s="2">
-        <v>170</v>
+        <v>176</v>
       </c>
       <c r="Y13" t="s" s="2">
+        <v>177</v>
+      </c>
+      <c r="Z13" t="s" s="2">
+        <v>178</v>
+      </c>
+      <c r="AA13" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="AB13" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="AC13" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="AD13" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="AE13" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="AF13" t="s" s="2">
         <v>171</v>
       </c>
-      <c r="Z13" t="s" s="2">
-        <v>172</v>
-      </c>
-      <c r="AA13" t="s" s="2">
-        <v>76</v>
-      </c>
-      <c r="AB13" t="s" s="2">
-        <v>76</v>
-      </c>
-      <c r="AC13" t="s" s="2">
-        <v>76</v>
-      </c>
-      <c r="AD13" t="s" s="2">
-        <v>76</v>
-      </c>
-      <c r="AE13" t="s" s="2">
-        <v>76</v>
-      </c>
-      <c r="AF13" t="s" s="2">
-        <v>166</v>
-      </c>
       <c r="AG13" t="s" s="2">
         <v>88</v>
       </c>
@@ -3420,7 +3478,7 @@
         <v>88</v>
       </c>
       <c r="AI13" t="s" s="2">
-        <v>76</v>
+        <v>154</v>
       </c>
       <c r="AJ13" t="s" s="2">
         <v>100</v>
@@ -3429,10 +3487,10 @@
         <v>76</v>
       </c>
       <c r="AL13" t="s" s="2">
-        <v>76</v>
+        <v>179</v>
       </c>
       <c r="AM13" t="s" s="2">
-        <v>76</v>
+        <v>180</v>
       </c>
       <c r="AN13" t="s" s="2">
         <v>76</v>
@@ -3440,10 +3498,10 @@
     </row>
     <row r="14" hidden="true">
       <c r="A14" t="s" s="2">
-        <v>173</v>
+        <v>181</v>
       </c>
       <c r="B14" t="s" s="2">
-        <v>173</v>
+        <v>181</v>
       </c>
       <c r="C14" s="2"/>
       <c r="D14" t="s" s="2">
@@ -3466,13 +3524,13 @@
         <v>76</v>
       </c>
       <c r="K14" t="s" s="2">
-        <v>174</v>
+        <v>182</v>
       </c>
       <c r="L14" t="s" s="2">
-        <v>175</v>
+        <v>183</v>
       </c>
       <c r="M14" t="s" s="2">
-        <v>176</v>
+        <v>184</v>
       </c>
       <c r="N14" s="2"/>
       <c r="O14" s="2"/>
@@ -3523,7 +3581,7 @@
         <v>76</v>
       </c>
       <c r="AF14" t="s" s="2">
-        <v>177</v>
+        <v>185</v>
       </c>
       <c r="AG14" t="s" s="2">
         <v>77</v>
@@ -3544,7 +3602,7 @@
         <v>76</v>
       </c>
       <c r="AM14" t="s" s="2">
-        <v>178</v>
+        <v>186</v>
       </c>
       <c r="AN14" t="s" s="2">
         <v>76</v>
@@ -3552,10 +3610,10 @@
     </row>
     <row r="15" hidden="true">
       <c r="A15" t="s" s="2">
-        <v>179</v>
+        <v>187</v>
       </c>
       <c r="B15" t="s" s="2">
-        <v>179</v>
+        <v>187</v>
       </c>
       <c r="C15" s="2"/>
       <c r="D15" t="s" s="2">
@@ -3584,7 +3642,7 @@
         <v>135</v>
       </c>
       <c r="M15" t="s" s="2">
-        <v>180</v>
+        <v>188</v>
       </c>
       <c r="N15" t="s" s="2">
         <v>137</v>
@@ -3625,19 +3683,19 @@
         <v>76</v>
       </c>
       <c r="AB15" t="s" s="2">
-        <v>181</v>
+        <v>138</v>
       </c>
       <c r="AC15" t="s" s="2">
-        <v>182</v>
+        <v>139</v>
       </c>
       <c r="AD15" t="s" s="2">
         <v>76</v>
       </c>
       <c r="AE15" t="s" s="2">
-        <v>183</v>
+        <v>140</v>
       </c>
       <c r="AF15" t="s" s="2">
-        <v>184</v>
+        <v>189</v>
       </c>
       <c r="AG15" t="s" s="2">
         <v>77</v>
@@ -3649,7 +3707,7 @@
         <v>76</v>
       </c>
       <c r="AJ15" t="s" s="2">
-        <v>139</v>
+        <v>142</v>
       </c>
       <c r="AK15" t="s" s="2">
         <v>76</v>
@@ -3658,7 +3716,7 @@
         <v>76</v>
       </c>
       <c r="AM15" t="s" s="2">
-        <v>178</v>
+        <v>186</v>
       </c>
       <c r="AN15" t="s" s="2">
         <v>76</v>
@@ -3666,10 +3724,10 @@
     </row>
     <row r="16">
       <c r="A16" t="s" s="2">
-        <v>185</v>
+        <v>190</v>
       </c>
       <c r="B16" t="s" s="2">
-        <v>185</v>
+        <v>190</v>
       </c>
       <c r="C16" s="2"/>
       <c r="D16" t="s" s="2">
@@ -3692,19 +3750,19 @@
         <v>89</v>
       </c>
       <c r="K16" t="s" s="2">
-        <v>186</v>
+        <v>191</v>
       </c>
       <c r="L16" t="s" s="2">
-        <v>187</v>
+        <v>192</v>
       </c>
       <c r="M16" t="s" s="2">
-        <v>188</v>
+        <v>193</v>
       </c>
       <c r="N16" t="s" s="2">
-        <v>189</v>
+        <v>194</v>
       </c>
       <c r="O16" t="s" s="2">
-        <v>190</v>
+        <v>195</v>
       </c>
       <c r="P16" t="s" s="2">
         <v>76</v>
@@ -3753,7 +3811,7 @@
         <v>76</v>
       </c>
       <c r="AF16" t="s" s="2">
-        <v>191</v>
+        <v>196</v>
       </c>
       <c r="AG16" t="s" s="2">
         <v>77</v>
@@ -3762,7 +3820,7 @@
         <v>78</v>
       </c>
       <c r="AI16" t="s" s="2">
-        <v>76</v>
+        <v>154</v>
       </c>
       <c r="AJ16" t="s" s="2">
         <v>100</v>
@@ -3771,10 +3829,10 @@
         <v>76</v>
       </c>
       <c r="AL16" t="s" s="2">
-        <v>192</v>
+        <v>197</v>
       </c>
       <c r="AM16" t="s" s="2">
-        <v>193</v>
+        <v>198</v>
       </c>
       <c r="AN16" t="s" s="2">
         <v>76</v>
@@ -3782,10 +3840,10 @@
     </row>
     <row r="17" hidden="true">
       <c r="A17" t="s" s="2">
-        <v>194</v>
+        <v>199</v>
       </c>
       <c r="B17" t="s" s="2">
-        <v>194</v>
+        <v>199</v>
       </c>
       <c r="C17" s="2"/>
       <c r="D17" t="s" s="2">
@@ -3808,13 +3866,13 @@
         <v>76</v>
       </c>
       <c r="K17" t="s" s="2">
-        <v>174</v>
+        <v>182</v>
       </c>
       <c r="L17" t="s" s="2">
-        <v>175</v>
+        <v>183</v>
       </c>
       <c r="M17" t="s" s="2">
-        <v>176</v>
+        <v>184</v>
       </c>
       <c r="N17" s="2"/>
       <c r="O17" s="2"/>
@@ -3865,7 +3923,7 @@
         <v>76</v>
       </c>
       <c r="AF17" t="s" s="2">
-        <v>177</v>
+        <v>185</v>
       </c>
       <c r="AG17" t="s" s="2">
         <v>77</v>
@@ -3886,7 +3944,7 @@
         <v>76</v>
       </c>
       <c r="AM17" t="s" s="2">
-        <v>178</v>
+        <v>186</v>
       </c>
       <c r="AN17" t="s" s="2">
         <v>76</v>
@@ -3894,10 +3952,10 @@
     </row>
     <row r="18" hidden="true">
       <c r="A18" t="s" s="2">
-        <v>195</v>
+        <v>200</v>
       </c>
       <c r="B18" t="s" s="2">
-        <v>195</v>
+        <v>200</v>
       </c>
       <c r="C18" s="2"/>
       <c r="D18" t="s" s="2">
@@ -3926,7 +3984,7 @@
         <v>135</v>
       </c>
       <c r="M18" t="s" s="2">
-        <v>180</v>
+        <v>188</v>
       </c>
       <c r="N18" t="s" s="2">
         <v>137</v>
@@ -3967,19 +4025,19 @@
         <v>76</v>
       </c>
       <c r="AB18" t="s" s="2">
-        <v>181</v>
+        <v>138</v>
       </c>
       <c r="AC18" t="s" s="2">
-        <v>182</v>
+        <v>139</v>
       </c>
       <c r="AD18" t="s" s="2">
         <v>76</v>
       </c>
       <c r="AE18" t="s" s="2">
-        <v>183</v>
+        <v>140</v>
       </c>
       <c r="AF18" t="s" s="2">
-        <v>184</v>
+        <v>189</v>
       </c>
       <c r="AG18" t="s" s="2">
         <v>77</v>
@@ -3991,7 +4049,7 @@
         <v>76</v>
       </c>
       <c r="AJ18" t="s" s="2">
-        <v>139</v>
+        <v>142</v>
       </c>
       <c r="AK18" t="s" s="2">
         <v>76</v>
@@ -4000,7 +4058,7 @@
         <v>76</v>
       </c>
       <c r="AM18" t="s" s="2">
-        <v>178</v>
+        <v>186</v>
       </c>
       <c r="AN18" t="s" s="2">
         <v>76</v>
@@ -4008,10 +4066,10 @@
     </row>
     <row r="19" hidden="true">
       <c r="A19" t="s" s="2">
-        <v>196</v>
+        <v>201</v>
       </c>
       <c r="B19" t="s" s="2">
-        <v>196</v>
+        <v>201</v>
       </c>
       <c r="C19" s="2"/>
       <c r="D19" t="s" s="2">
@@ -4037,23 +4095,23 @@
         <v>102</v>
       </c>
       <c r="L19" t="s" s="2">
-        <v>197</v>
+        <v>202</v>
       </c>
       <c r="M19" t="s" s="2">
-        <v>198</v>
+        <v>203</v>
       </c>
       <c r="N19" t="s" s="2">
-        <v>199</v>
+        <v>204</v>
       </c>
       <c r="O19" t="s" s="2">
-        <v>200</v>
+        <v>205</v>
       </c>
       <c r="P19" t="s" s="2">
         <v>76</v>
       </c>
       <c r="Q19" s="2"/>
       <c r="R19" t="s" s="2">
-        <v>201</v>
+        <v>206</v>
       </c>
       <c r="S19" t="s" s="2">
         <v>76</v>
@@ -4095,7 +4153,7 @@
         <v>76</v>
       </c>
       <c r="AF19" t="s" s="2">
-        <v>202</v>
+        <v>207</v>
       </c>
       <c r="AG19" t="s" s="2">
         <v>77</v>
@@ -4113,10 +4171,10 @@
         <v>76</v>
       </c>
       <c r="AL19" t="s" s="2">
-        <v>203</v>
+        <v>208</v>
       </c>
       <c r="AM19" t="s" s="2">
-        <v>204</v>
+        <v>209</v>
       </c>
       <c r="AN19" t="s" s="2">
         <v>76</v>
@@ -4124,10 +4182,10 @@
     </row>
     <row r="20" hidden="true">
       <c r="A20" t="s" s="2">
-        <v>205</v>
+        <v>210</v>
       </c>
       <c r="B20" t="s" s="2">
-        <v>205</v>
+        <v>210</v>
       </c>
       <c r="C20" s="2"/>
       <c r="D20" t="s" s="2">
@@ -4150,16 +4208,16 @@
         <v>89</v>
       </c>
       <c r="K20" t="s" s="2">
-        <v>174</v>
+        <v>182</v>
       </c>
       <c r="L20" t="s" s="2">
-        <v>206</v>
+        <v>211</v>
       </c>
       <c r="M20" t="s" s="2">
-        <v>207</v>
+        <v>212</v>
       </c>
       <c r="N20" t="s" s="2">
-        <v>208</v>
+        <v>213</v>
       </c>
       <c r="O20" s="2"/>
       <c r="P20" t="s" s="2">
@@ -4209,7 +4267,7 @@
         <v>76</v>
       </c>
       <c r="AF20" t="s" s="2">
-        <v>209</v>
+        <v>214</v>
       </c>
       <c r="AG20" t="s" s="2">
         <v>77</v>
@@ -4227,10 +4285,10 @@
         <v>76</v>
       </c>
       <c r="AL20" t="s" s="2">
-        <v>210</v>
+        <v>215</v>
       </c>
       <c r="AM20" t="s" s="2">
-        <v>211</v>
+        <v>216</v>
       </c>
       <c r="AN20" t="s" s="2">
         <v>76</v>
@@ -4238,10 +4296,10 @@
     </row>
     <row r="21" hidden="true">
       <c r="A21" t="s" s="2">
-        <v>212</v>
+        <v>217</v>
       </c>
       <c r="B21" t="s" s="2">
-        <v>212</v>
+        <v>217</v>
       </c>
       <c r="C21" s="2"/>
       <c r="D21" t="s" s="2">
@@ -4267,21 +4325,21 @@
         <v>108</v>
       </c>
       <c r="L21" t="s" s="2">
-        <v>213</v>
+        <v>218</v>
       </c>
       <c r="M21" t="s" s="2">
-        <v>214</v>
+        <v>219</v>
       </c>
       <c r="N21" s="2"/>
       <c r="O21" t="s" s="2">
-        <v>215</v>
+        <v>220</v>
       </c>
       <c r="P21" t="s" s="2">
         <v>76</v>
       </c>
       <c r="Q21" s="2"/>
       <c r="R21" t="s" s="2">
-        <v>216</v>
+        <v>221</v>
       </c>
       <c r="S21" t="s" s="2">
         <v>76</v>
@@ -4323,7 +4381,7 @@
         <v>76</v>
       </c>
       <c r="AF21" t="s" s="2">
-        <v>217</v>
+        <v>222</v>
       </c>
       <c r="AG21" t="s" s="2">
         <v>77</v>
@@ -4341,10 +4399,10 @@
         <v>76</v>
       </c>
       <c r="AL21" t="s" s="2">
-        <v>218</v>
+        <v>223</v>
       </c>
       <c r="AM21" t="s" s="2">
-        <v>219</v>
+        <v>224</v>
       </c>
       <c r="AN21" t="s" s="2">
         <v>76</v>
@@ -4352,10 +4410,10 @@
     </row>
     <row r="22" hidden="true">
       <c r="A22" t="s" s="2">
-        <v>220</v>
+        <v>225</v>
       </c>
       <c r="B22" t="s" s="2">
-        <v>220</v>
+        <v>225</v>
       </c>
       <c r="C22" s="2"/>
       <c r="D22" t="s" s="2">
@@ -4378,24 +4436,26 @@
         <v>89</v>
       </c>
       <c r="K22" t="s" s="2">
-        <v>174</v>
+        <v>182</v>
       </c>
       <c r="L22" t="s" s="2">
-        <v>221</v>
+        <v>226</v>
       </c>
       <c r="M22" t="s" s="2">
-        <v>222</v>
-      </c>
-      <c r="N22" s="2"/>
+        <v>227</v>
+      </c>
+      <c r="N22" t="s" s="2">
+        <v>228</v>
+      </c>
       <c r="O22" t="s" s="2">
-        <v>223</v>
+        <v>229</v>
       </c>
       <c r="P22" t="s" s="2">
         <v>76</v>
       </c>
       <c r="Q22" s="2"/>
       <c r="R22" t="s" s="2">
-        <v>224</v>
+        <v>230</v>
       </c>
       <c r="S22" t="s" s="2">
         <v>76</v>
@@ -4437,7 +4497,7 @@
         <v>76</v>
       </c>
       <c r="AF22" t="s" s="2">
-        <v>225</v>
+        <v>231</v>
       </c>
       <c r="AG22" t="s" s="2">
         <v>77</v>
@@ -4455,10 +4515,10 @@
         <v>76</v>
       </c>
       <c r="AL22" t="s" s="2">
-        <v>226</v>
+        <v>232</v>
       </c>
       <c r="AM22" t="s" s="2">
-        <v>227</v>
+        <v>233</v>
       </c>
       <c r="AN22" t="s" s="2">
         <v>76</v>
@@ -4466,10 +4526,10 @@
     </row>
     <row r="23" hidden="true">
       <c r="A23" t="s" s="2">
-        <v>228</v>
+        <v>234</v>
       </c>
       <c r="B23" t="s" s="2">
-        <v>228</v>
+        <v>234</v>
       </c>
       <c r="C23" s="2"/>
       <c r="D23" t="s" s="2">
@@ -4492,19 +4552,19 @@
         <v>89</v>
       </c>
       <c r="K23" t="s" s="2">
-        <v>229</v>
+        <v>235</v>
       </c>
       <c r="L23" t="s" s="2">
-        <v>230</v>
+        <v>236</v>
       </c>
       <c r="M23" t="s" s="2">
-        <v>231</v>
+        <v>237</v>
       </c>
       <c r="N23" t="s" s="2">
-        <v>232</v>
+        <v>238</v>
       </c>
       <c r="O23" t="s" s="2">
-        <v>233</v>
+        <v>239</v>
       </c>
       <c r="P23" t="s" s="2">
         <v>76</v>
@@ -4553,7 +4613,7 @@
         <v>76</v>
       </c>
       <c r="AF23" t="s" s="2">
-        <v>234</v>
+        <v>240</v>
       </c>
       <c r="AG23" t="s" s="2">
         <v>77</v>
@@ -4571,10 +4631,10 @@
         <v>76</v>
       </c>
       <c r="AL23" t="s" s="2">
-        <v>235</v>
+        <v>241</v>
       </c>
       <c r="AM23" t="s" s="2">
-        <v>236</v>
+        <v>242</v>
       </c>
       <c r="AN23" t="s" s="2">
         <v>76</v>
@@ -4582,10 +4642,10 @@
     </row>
     <row r="24" hidden="true">
       <c r="A24" t="s" s="2">
-        <v>237</v>
+        <v>243</v>
       </c>
       <c r="B24" t="s" s="2">
-        <v>237</v>
+        <v>243</v>
       </c>
       <c r="C24" s="2"/>
       <c r="D24" t="s" s="2">
@@ -4608,19 +4668,19 @@
         <v>89</v>
       </c>
       <c r="K24" t="s" s="2">
-        <v>174</v>
+        <v>182</v>
       </c>
       <c r="L24" t="s" s="2">
-        <v>238</v>
+        <v>244</v>
       </c>
       <c r="M24" t="s" s="2">
-        <v>239</v>
+        <v>245</v>
       </c>
       <c r="N24" t="s" s="2">
-        <v>240</v>
+        <v>246</v>
       </c>
       <c r="O24" t="s" s="2">
-        <v>241</v>
+        <v>247</v>
       </c>
       <c r="P24" t="s" s="2">
         <v>76</v>
@@ -4669,7 +4729,7 @@
         <v>76</v>
       </c>
       <c r="AF24" t="s" s="2">
-        <v>242</v>
+        <v>248</v>
       </c>
       <c r="AG24" t="s" s="2">
         <v>77</v>
@@ -4687,10 +4747,10 @@
         <v>76</v>
       </c>
       <c r="AL24" t="s" s="2">
-        <v>243</v>
+        <v>249</v>
       </c>
       <c r="AM24" t="s" s="2">
-        <v>244</v>
+        <v>250</v>
       </c>
       <c r="AN24" t="s" s="2">
         <v>76</v>
@@ -4698,10 +4758,10 @@
     </row>
     <row r="25">
       <c r="A25" t="s" s="2">
-        <v>245</v>
+        <v>251</v>
       </c>
       <c r="B25" t="s" s="2">
-        <v>245</v>
+        <v>251</v>
       </c>
       <c r="C25" s="2"/>
       <c r="D25" t="s" s="2">
@@ -4724,15 +4784,17 @@
         <v>89</v>
       </c>
       <c r="K25" t="s" s="2">
-        <v>167</v>
+        <v>172</v>
       </c>
       <c r="L25" t="s" s="2">
-        <v>246</v>
+        <v>252</v>
       </c>
       <c r="M25" t="s" s="2">
-        <v>247</v>
-      </c>
-      <c r="N25" s="2"/>
+        <v>253</v>
+      </c>
+      <c r="N25" t="s" s="2">
+        <v>175</v>
+      </c>
       <c r="O25" s="2"/>
       <c r="P25" t="s" s="2">
         <v>76</v>
@@ -4757,11 +4819,11 @@
         <v>76</v>
       </c>
       <c r="X25" t="s" s="2">
-        <v>159</v>
+        <v>164</v>
       </c>
       <c r="Y25" s="2"/>
       <c r="Z25" t="s" s="2">
-        <v>248</v>
+        <v>254</v>
       </c>
       <c r="AA25" t="s" s="2">
         <v>76</v>
@@ -4779,7 +4841,7 @@
         <v>76</v>
       </c>
       <c r="AF25" t="s" s="2">
-        <v>245</v>
+        <v>251</v>
       </c>
       <c r="AG25" t="s" s="2">
         <v>88</v>
@@ -4788,30 +4850,30 @@
         <v>78</v>
       </c>
       <c r="AI25" t="s" s="2">
-        <v>76</v>
+        <v>154</v>
       </c>
       <c r="AJ25" t="s" s="2">
         <v>100</v>
       </c>
       <c r="AK25" t="s" s="2">
-        <v>249</v>
+        <v>255</v>
       </c>
       <c r="AL25" t="s" s="2">
-        <v>250</v>
+        <v>256</v>
       </c>
       <c r="AM25" t="s" s="2">
-        <v>251</v>
+        <v>257</v>
       </c>
       <c r="AN25" t="s" s="2">
-        <v>252</v>
+        <v>258</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="s" s="2">
-        <v>253</v>
+        <v>259</v>
       </c>
       <c r="B26" t="s" s="2">
-        <v>253</v>
+        <v>259</v>
       </c>
       <c r="C26" s="2"/>
       <c r="D26" t="s" s="2">
@@ -4834,16 +4896,16 @@
         <v>89</v>
       </c>
       <c r="K26" t="s" s="2">
-        <v>254</v>
+        <v>260</v>
       </c>
       <c r="L26" t="s" s="2">
-        <v>255</v>
+        <v>261</v>
       </c>
       <c r="M26" t="s" s="2">
-        <v>256</v>
+        <v>262</v>
       </c>
       <c r="N26" t="s" s="2">
-        <v>257</v>
+        <v>263</v>
       </c>
       <c r="O26" s="2"/>
       <c r="P26" t="s" s="2">
@@ -4893,7 +4955,7 @@
         <v>76</v>
       </c>
       <c r="AF26" t="s" s="2">
-        <v>253</v>
+        <v>259</v>
       </c>
       <c r="AG26" t="s" s="2">
         <v>77</v>
@@ -4902,30 +4964,30 @@
         <v>88</v>
       </c>
       <c r="AI26" t="s" s="2">
-        <v>76</v>
+        <v>154</v>
       </c>
       <c r="AJ26" t="s" s="2">
-        <v>100</v>
+        <v>264</v>
       </c>
       <c r="AK26" t="s" s="2">
-        <v>258</v>
+        <v>265</v>
       </c>
       <c r="AL26" t="s" s="2">
         <v>76</v>
       </c>
       <c r="AM26" t="s" s="2">
-        <v>259</v>
+        <v>266</v>
       </c>
       <c r="AN26" t="s" s="2">
-        <v>260</v>
+        <v>267</v>
       </c>
     </row>
     <row r="27" hidden="true">
       <c r="A27" t="s" s="2">
-        <v>261</v>
+        <v>268</v>
       </c>
       <c r="B27" t="s" s="2">
-        <v>261</v>
+        <v>268</v>
       </c>
       <c r="C27" s="2"/>
       <c r="D27" t="s" s="2">
@@ -4948,13 +5010,13 @@
         <v>76</v>
       </c>
       <c r="K27" t="s" s="2">
-        <v>174</v>
+        <v>182</v>
       </c>
       <c r="L27" t="s" s="2">
-        <v>175</v>
+        <v>183</v>
       </c>
       <c r="M27" t="s" s="2">
-        <v>176</v>
+        <v>184</v>
       </c>
       <c r="N27" s="2"/>
       <c r="O27" s="2"/>
@@ -5005,7 +5067,7 @@
         <v>76</v>
       </c>
       <c r="AF27" t="s" s="2">
-        <v>177</v>
+        <v>185</v>
       </c>
       <c r="AG27" t="s" s="2">
         <v>77</v>
@@ -5026,7 +5088,7 @@
         <v>76</v>
       </c>
       <c r="AM27" t="s" s="2">
-        <v>178</v>
+        <v>186</v>
       </c>
       <c r="AN27" t="s" s="2">
         <v>76</v>
@@ -5034,10 +5096,10 @@
     </row>
     <row r="28" hidden="true">
       <c r="A28" t="s" s="2">
-        <v>262</v>
+        <v>269</v>
       </c>
       <c r="B28" t="s" s="2">
-        <v>262</v>
+        <v>269</v>
       </c>
       <c r="C28" s="2"/>
       <c r="D28" t="s" s="2">
@@ -5066,7 +5128,7 @@
         <v>135</v>
       </c>
       <c r="M28" t="s" s="2">
-        <v>180</v>
+        <v>188</v>
       </c>
       <c r="N28" t="s" s="2">
         <v>137</v>
@@ -5107,19 +5169,19 @@
         <v>76</v>
       </c>
       <c r="AB28" t="s" s="2">
-        <v>181</v>
+        <v>138</v>
       </c>
       <c r="AC28" t="s" s="2">
-        <v>182</v>
+        <v>139</v>
       </c>
       <c r="AD28" t="s" s="2">
         <v>76</v>
       </c>
       <c r="AE28" t="s" s="2">
-        <v>183</v>
+        <v>140</v>
       </c>
       <c r="AF28" t="s" s="2">
-        <v>184</v>
+        <v>189</v>
       </c>
       <c r="AG28" t="s" s="2">
         <v>77</v>
@@ -5131,7 +5193,7 @@
         <v>76</v>
       </c>
       <c r="AJ28" t="s" s="2">
-        <v>139</v>
+        <v>142</v>
       </c>
       <c r="AK28" t="s" s="2">
         <v>76</v>
@@ -5140,7 +5202,7 @@
         <v>76</v>
       </c>
       <c r="AM28" t="s" s="2">
-        <v>178</v>
+        <v>186</v>
       </c>
       <c r="AN28" t="s" s="2">
         <v>76</v>
@@ -5148,10 +5210,10 @@
     </row>
     <row r="29" hidden="true">
       <c r="A29" t="s" s="2">
-        <v>263</v>
+        <v>270</v>
       </c>
       <c r="B29" t="s" s="2">
-        <v>263</v>
+        <v>270</v>
       </c>
       <c r="C29" s="2"/>
       <c r="D29" t="s" s="2">
@@ -5174,16 +5236,16 @@
         <v>89</v>
       </c>
       <c r="K29" t="s" s="2">
-        <v>174</v>
+        <v>182</v>
       </c>
       <c r="L29" t="s" s="2">
-        <v>264</v>
+        <v>271</v>
       </c>
       <c r="M29" t="s" s="2">
-        <v>265</v>
+        <v>272</v>
       </c>
       <c r="N29" t="s" s="2">
-        <v>266</v>
+        <v>273</v>
       </c>
       <c r="O29" s="2"/>
       <c r="P29" t="s" s="2">
@@ -5233,7 +5295,7 @@
         <v>76</v>
       </c>
       <c r="AF29" t="s" s="2">
-        <v>267</v>
+        <v>274</v>
       </c>
       <c r="AG29" t="s" s="2">
         <v>77</v>
@@ -5242,7 +5304,7 @@
         <v>88</v>
       </c>
       <c r="AI29" t="s" s="2">
-        <v>268</v>
+        <v>275</v>
       </c>
       <c r="AJ29" t="s" s="2">
         <v>100</v>
@@ -5262,10 +5324,10 @@
     </row>
     <row r="30" hidden="true">
       <c r="A30" t="s" s="2">
-        <v>269</v>
+        <v>276</v>
       </c>
       <c r="B30" t="s" s="2">
-        <v>269</v>
+        <v>276</v>
       </c>
       <c r="C30" s="2"/>
       <c r="D30" t="s" s="2">
@@ -5291,13 +5353,13 @@
         <v>102</v>
       </c>
       <c r="L30" t="s" s="2">
-        <v>270</v>
+        <v>277</v>
       </c>
       <c r="M30" t="s" s="2">
-        <v>271</v>
+        <v>278</v>
       </c>
       <c r="N30" t="s" s="2">
-        <v>272</v>
+        <v>279</v>
       </c>
       <c r="O30" s="2"/>
       <c r="P30" t="s" s="2">
@@ -5323,13 +5385,13 @@
         <v>76</v>
       </c>
       <c r="X30" t="s" s="2">
-        <v>170</v>
+        <v>176</v>
       </c>
       <c r="Y30" t="s" s="2">
-        <v>273</v>
+        <v>280</v>
       </c>
       <c r="Z30" t="s" s="2">
-        <v>274</v>
+        <v>281</v>
       </c>
       <c r="AA30" t="s" s="2">
         <v>76</v>
@@ -5347,7 +5409,7 @@
         <v>76</v>
       </c>
       <c r="AF30" t="s" s="2">
-        <v>275</v>
+        <v>282</v>
       </c>
       <c r="AG30" t="s" s="2">
         <v>77</v>
@@ -5376,10 +5438,10 @@
     </row>
     <row r="31">
       <c r="A31" t="s" s="2">
-        <v>276</v>
+        <v>283</v>
       </c>
       <c r="B31" t="s" s="2">
-        <v>276</v>
+        <v>283</v>
       </c>
       <c r="C31" s="2"/>
       <c r="D31" t="s" s="2">
@@ -5402,16 +5464,16 @@
         <v>89</v>
       </c>
       <c r="K31" t="s" s="2">
-        <v>277</v>
+        <v>284</v>
       </c>
       <c r="L31" t="s" s="2">
-        <v>278</v>
+        <v>285</v>
       </c>
       <c r="M31" t="s" s="2">
-        <v>279</v>
+        <v>286</v>
       </c>
       <c r="N31" t="s" s="2">
-        <v>280</v>
+        <v>287</v>
       </c>
       <c r="O31" s="2"/>
       <c r="P31" t="s" s="2">
@@ -5461,7 +5523,7 @@
         <v>76</v>
       </c>
       <c r="AF31" t="s" s="2">
-        <v>281</v>
+        <v>288</v>
       </c>
       <c r="AG31" t="s" s="2">
         <v>77</v>
@@ -5470,7 +5532,7 @@
         <v>88</v>
       </c>
       <c r="AI31" t="s" s="2">
-        <v>76</v>
+        <v>154</v>
       </c>
       <c r="AJ31" t="s" s="2">
         <v>100</v>
@@ -5479,10 +5541,10 @@
         <v>76</v>
       </c>
       <c r="AL31" t="s" s="2">
-        <v>76</v>
+        <v>156</v>
       </c>
       <c r="AM31" t="s" s="2">
-        <v>282</v>
+        <v>289</v>
       </c>
       <c r="AN31" t="s" s="2">
         <v>76</v>
@@ -5490,10 +5552,10 @@
     </row>
     <row r="32" hidden="true">
       <c r="A32" t="s" s="2">
-        <v>283</v>
+        <v>290</v>
       </c>
       <c r="B32" t="s" s="2">
-        <v>283</v>
+        <v>290</v>
       </c>
       <c r="C32" s="2"/>
       <c r="D32" t="s" s="2">
@@ -5516,13 +5578,13 @@
         <v>76</v>
       </c>
       <c r="K32" t="s" s="2">
-        <v>174</v>
+        <v>182</v>
       </c>
       <c r="L32" t="s" s="2">
-        <v>175</v>
+        <v>183</v>
       </c>
       <c r="M32" t="s" s="2">
-        <v>176</v>
+        <v>184</v>
       </c>
       <c r="N32" s="2"/>
       <c r="O32" s="2"/>
@@ -5573,7 +5635,7 @@
         <v>76</v>
       </c>
       <c r="AF32" t="s" s="2">
-        <v>177</v>
+        <v>185</v>
       </c>
       <c r="AG32" t="s" s="2">
         <v>77</v>
@@ -5594,7 +5656,7 @@
         <v>76</v>
       </c>
       <c r="AM32" t="s" s="2">
-        <v>178</v>
+        <v>186</v>
       </c>
       <c r="AN32" t="s" s="2">
         <v>76</v>
@@ -5602,10 +5664,10 @@
     </row>
     <row r="33" hidden="true">
       <c r="A33" t="s" s="2">
-        <v>284</v>
+        <v>291</v>
       </c>
       <c r="B33" t="s" s="2">
-        <v>284</v>
+        <v>291</v>
       </c>
       <c r="C33" s="2"/>
       <c r="D33" t="s" s="2">
@@ -5634,7 +5696,7 @@
         <v>135</v>
       </c>
       <c r="M33" t="s" s="2">
-        <v>180</v>
+        <v>188</v>
       </c>
       <c r="N33" t="s" s="2">
         <v>137</v>
@@ -5675,19 +5737,19 @@
         <v>76</v>
       </c>
       <c r="AB33" t="s" s="2">
-        <v>181</v>
+        <v>138</v>
       </c>
       <c r="AC33" t="s" s="2">
-        <v>182</v>
+        <v>139</v>
       </c>
       <c r="AD33" t="s" s="2">
         <v>76</v>
       </c>
       <c r="AE33" t="s" s="2">
-        <v>183</v>
+        <v>140</v>
       </c>
       <c r="AF33" t="s" s="2">
-        <v>184</v>
+        <v>189</v>
       </c>
       <c r="AG33" t="s" s="2">
         <v>77</v>
@@ -5699,7 +5761,7 @@
         <v>76</v>
       </c>
       <c r="AJ33" t="s" s="2">
-        <v>139</v>
+        <v>142</v>
       </c>
       <c r="AK33" t="s" s="2">
         <v>76</v>
@@ -5708,7 +5770,7 @@
         <v>76</v>
       </c>
       <c r="AM33" t="s" s="2">
-        <v>178</v>
+        <v>186</v>
       </c>
       <c r="AN33" t="s" s="2">
         <v>76</v>
@@ -5716,10 +5778,10 @@
     </row>
     <row r="34" hidden="true">
       <c r="A34" t="s" s="2">
-        <v>285</v>
+        <v>292</v>
       </c>
       <c r="B34" t="s" s="2">
-        <v>285</v>
+        <v>292</v>
       </c>
       <c r="C34" s="2"/>
       <c r="D34" t="s" s="2">
@@ -5745,16 +5807,16 @@
         <v>108</v>
       </c>
       <c r="L34" t="s" s="2">
-        <v>286</v>
+        <v>293</v>
       </c>
       <c r="M34" t="s" s="2">
-        <v>287</v>
+        <v>294</v>
       </c>
       <c r="N34" t="s" s="2">
-        <v>288</v>
+        <v>295</v>
       </c>
       <c r="O34" t="s" s="2">
-        <v>289</v>
+        <v>296</v>
       </c>
       <c r="P34" t="s" s="2">
         <v>76</v>
@@ -5779,13 +5841,13 @@
         <v>76</v>
       </c>
       <c r="X34" t="s" s="2">
-        <v>159</v>
+        <v>164</v>
       </c>
       <c r="Y34" t="s" s="2">
-        <v>290</v>
+        <v>297</v>
       </c>
       <c r="Z34" t="s" s="2">
-        <v>291</v>
+        <v>298</v>
       </c>
       <c r="AA34" t="s" s="2">
         <v>76</v>
@@ -5803,7 +5865,7 @@
         <v>76</v>
       </c>
       <c r="AF34" t="s" s="2">
-        <v>292</v>
+        <v>299</v>
       </c>
       <c r="AG34" t="s" s="2">
         <v>77</v>
@@ -5824,7 +5886,7 @@
         <v>131</v>
       </c>
       <c r="AM34" t="s" s="2">
-        <v>293</v>
+        <v>300</v>
       </c>
       <c r="AN34" t="s" s="2">
         <v>76</v>
@@ -5832,10 +5894,10 @@
     </row>
     <row r="35" hidden="true">
       <c r="A35" t="s" s="2">
-        <v>294</v>
+        <v>301</v>
       </c>
       <c r="B35" t="s" s="2">
-        <v>294</v>
+        <v>301</v>
       </c>
       <c r="C35" s="2"/>
       <c r="D35" t="s" s="2">
@@ -5858,19 +5920,19 @@
         <v>89</v>
       </c>
       <c r="K35" t="s" s="2">
-        <v>167</v>
+        <v>172</v>
       </c>
       <c r="L35" t="s" s="2">
-        <v>295</v>
+        <v>302</v>
       </c>
       <c r="M35" t="s" s="2">
-        <v>296</v>
+        <v>303</v>
       </c>
       <c r="N35" t="s" s="2">
-        <v>297</v>
+        <v>304</v>
       </c>
       <c r="O35" t="s" s="2">
-        <v>298</v>
+        <v>305</v>
       </c>
       <c r="P35" t="s" s="2">
         <v>76</v>
@@ -5880,7 +5942,7 @@
         <v>76</v>
       </c>
       <c r="S35" t="s" s="2">
-        <v>299</v>
+        <v>306</v>
       </c>
       <c r="T35" t="s" s="2">
         <v>76</v>
@@ -5895,52 +5957,52 @@
         <v>76</v>
       </c>
       <c r="X35" t="s" s="2">
-        <v>170</v>
+        <v>176</v>
       </c>
       <c r="Y35" t="s" s="2">
+        <v>307</v>
+      </c>
+      <c r="Z35" t="s" s="2">
+        <v>308</v>
+      </c>
+      <c r="AA35" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="AB35" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="AC35" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="AD35" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="AE35" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="AF35" t="s" s="2">
+        <v>309</v>
+      </c>
+      <c r="AG35" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AH35" t="s" s="2">
+        <v>88</v>
+      </c>
+      <c r="AI35" t="s" s="2">
+        <v>154</v>
+      </c>
+      <c r="AJ35" t="s" s="2">
+        <v>310</v>
+      </c>
+      <c r="AK35" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="AL35" t="s" s="2">
+        <v>311</v>
+      </c>
+      <c r="AM35" t="s" s="2">
         <v>300</v>
-      </c>
-      <c r="Z35" t="s" s="2">
-        <v>301</v>
-      </c>
-      <c r="AA35" t="s" s="2">
-        <v>76</v>
-      </c>
-      <c r="AB35" t="s" s="2">
-        <v>76</v>
-      </c>
-      <c r="AC35" t="s" s="2">
-        <v>76</v>
-      </c>
-      <c r="AD35" t="s" s="2">
-        <v>76</v>
-      </c>
-      <c r="AE35" t="s" s="2">
-        <v>76</v>
-      </c>
-      <c r="AF35" t="s" s="2">
-        <v>302</v>
-      </c>
-      <c r="AG35" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="AH35" t="s" s="2">
-        <v>88</v>
-      </c>
-      <c r="AI35" t="s" s="2">
-        <v>76</v>
-      </c>
-      <c r="AJ35" t="s" s="2">
-        <v>303</v>
-      </c>
-      <c r="AK35" t="s" s="2">
-        <v>76</v>
-      </c>
-      <c r="AL35" t="s" s="2">
-        <v>304</v>
-      </c>
-      <c r="AM35" t="s" s="2">
-        <v>293</v>
       </c>
       <c r="AN35" t="s" s="2">
         <v>76</v>
@@ -5948,10 +6010,10 @@
     </row>
     <row r="36" hidden="true">
       <c r="A36" t="s" s="2">
-        <v>305</v>
+        <v>312</v>
       </c>
       <c r="B36" t="s" s="2">
-        <v>305</v>
+        <v>312</v>
       </c>
       <c r="C36" s="2"/>
       <c r="D36" t="s" s="2">
@@ -5977,29 +6039,29 @@
         <v>102</v>
       </c>
       <c r="L36" t="s" s="2">
-        <v>306</v>
+        <v>313</v>
       </c>
       <c r="M36" t="s" s="2">
-        <v>307</v>
+        <v>314</v>
       </c>
       <c r="N36" t="s" s="2">
-        <v>308</v>
+        <v>315</v>
       </c>
       <c r="O36" t="s" s="2">
-        <v>309</v>
+        <v>316</v>
       </c>
       <c r="P36" t="s" s="2">
         <v>76</v>
       </c>
       <c r="Q36" s="2"/>
       <c r="R36" t="s" s="2">
-        <v>310</v>
+        <v>317</v>
       </c>
       <c r="S36" t="s" s="2">
         <v>76</v>
       </c>
       <c r="T36" t="s" s="2">
-        <v>311</v>
+        <v>318</v>
       </c>
       <c r="U36" t="s" s="2">
         <v>76</v>
@@ -6035,7 +6097,7 @@
         <v>76</v>
       </c>
       <c r="AF36" t="s" s="2">
-        <v>312</v>
+        <v>319</v>
       </c>
       <c r="AG36" t="s" s="2">
         <v>77</v>
@@ -6053,10 +6115,10 @@
         <v>76</v>
       </c>
       <c r="AL36" t="s" s="2">
-        <v>313</v>
+        <v>320</v>
       </c>
       <c r="AM36" t="s" s="2">
-        <v>314</v>
+        <v>321</v>
       </c>
       <c r="AN36" t="s" s="2">
         <v>76</v>
@@ -6064,10 +6126,10 @@
     </row>
     <row r="37" hidden="true">
       <c r="A37" t="s" s="2">
-        <v>315</v>
+        <v>322</v>
       </c>
       <c r="B37" t="s" s="2">
-        <v>315</v>
+        <v>322</v>
       </c>
       <c r="C37" s="2"/>
       <c r="D37" t="s" s="2">
@@ -6090,16 +6152,16 @@
         <v>89</v>
       </c>
       <c r="K37" t="s" s="2">
-        <v>174</v>
+        <v>182</v>
       </c>
       <c r="L37" t="s" s="2">
-        <v>316</v>
+        <v>323</v>
       </c>
       <c r="M37" t="s" s="2">
-        <v>317</v>
+        <v>324</v>
       </c>
       <c r="N37" t="s" s="2">
-        <v>318</v>
+        <v>325</v>
       </c>
       <c r="O37" s="2"/>
       <c r="P37" t="s" s="2">
@@ -6113,7 +6175,7 @@
         <v>76</v>
       </c>
       <c r="T37" t="s" s="2">
-        <v>319</v>
+        <v>326</v>
       </c>
       <c r="U37" t="s" s="2">
         <v>76</v>
@@ -6149,7 +6211,7 @@
         <v>76</v>
       </c>
       <c r="AF37" t="s" s="2">
-        <v>320</v>
+        <v>327</v>
       </c>
       <c r="AG37" t="s" s="2">
         <v>77</v>
@@ -6161,16 +6223,16 @@
         <v>76</v>
       </c>
       <c r="AJ37" t="s" s="2">
-        <v>321</v>
+        <v>328</v>
       </c>
       <c r="AK37" t="s" s="2">
         <v>76</v>
       </c>
       <c r="AL37" t="s" s="2">
-        <v>322</v>
+        <v>329</v>
       </c>
       <c r="AM37" t="s" s="2">
-        <v>323</v>
+        <v>330</v>
       </c>
       <c r="AN37" t="s" s="2">
         <v>76</v>
@@ -6178,10 +6240,10 @@
     </row>
     <row r="38" hidden="true">
       <c r="A38" t="s" s="2">
-        <v>324</v>
+        <v>331</v>
       </c>
       <c r="B38" t="s" s="2">
-        <v>324</v>
+        <v>331</v>
       </c>
       <c r="C38" s="2"/>
       <c r="D38" t="s" s="2">
@@ -6204,15 +6266,17 @@
         <v>89</v>
       </c>
       <c r="K38" t="s" s="2">
-        <v>325</v>
+        <v>332</v>
       </c>
       <c r="L38" t="s" s="2">
-        <v>326</v>
+        <v>333</v>
       </c>
       <c r="M38" t="s" s="2">
-        <v>327</v>
-      </c>
-      <c r="N38" s="2"/>
+        <v>334</v>
+      </c>
+      <c r="N38" t="s" s="2">
+        <v>335</v>
+      </c>
       <c r="O38" s="2"/>
       <c r="P38" t="s" s="2">
         <v>76</v>
@@ -6261,7 +6325,7 @@
         <v>76</v>
       </c>
       <c r="AF38" t="s" s="2">
-        <v>328</v>
+        <v>336</v>
       </c>
       <c r="AG38" t="s" s="2">
         <v>77</v>
@@ -6270,19 +6334,19 @@
         <v>88</v>
       </c>
       <c r="AI38" t="s" s="2">
-        <v>76</v>
+        <v>154</v>
       </c>
       <c r="AJ38" t="s" s="2">
-        <v>100</v>
+        <v>337</v>
       </c>
       <c r="AK38" t="s" s="2">
         <v>76</v>
       </c>
       <c r="AL38" t="s" s="2">
-        <v>329</v>
+        <v>338</v>
       </c>
       <c r="AM38" t="s" s="2">
-        <v>330</v>
+        <v>339</v>
       </c>
       <c r="AN38" t="s" s="2">
         <v>76</v>
@@ -6290,10 +6354,10 @@
     </row>
     <row r="39">
       <c r="A39" t="s" s="2">
-        <v>331</v>
+        <v>340</v>
       </c>
       <c r="B39" t="s" s="2">
-        <v>331</v>
+        <v>340</v>
       </c>
       <c r="C39" s="2"/>
       <c r="D39" t="s" s="2">
@@ -6316,16 +6380,16 @@
         <v>89</v>
       </c>
       <c r="K39" t="s" s="2">
-        <v>332</v>
+        <v>341</v>
       </c>
       <c r="L39" t="s" s="2">
-        <v>333</v>
+        <v>342</v>
       </c>
       <c r="M39" t="s" s="2">
-        <v>334</v>
+        <v>343</v>
       </c>
       <c r="N39" t="s" s="2">
-        <v>335</v>
+        <v>344</v>
       </c>
       <c r="O39" s="2"/>
       <c r="P39" t="s" s="2">
@@ -6375,7 +6439,7 @@
         <v>76</v>
       </c>
       <c r="AF39" t="s" s="2">
-        <v>336</v>
+        <v>345</v>
       </c>
       <c r="AG39" t="s" s="2">
         <v>77</v>
@@ -6384,19 +6448,19 @@
         <v>88</v>
       </c>
       <c r="AI39" t="s" s="2">
-        <v>76</v>
+        <v>154</v>
       </c>
       <c r="AJ39" t="s" s="2">
-        <v>100</v>
+        <v>264</v>
       </c>
       <c r="AK39" t="s" s="2">
         <v>76</v>
       </c>
       <c r="AL39" t="s" s="2">
-        <v>337</v>
+        <v>346</v>
       </c>
       <c r="AM39" t="s" s="2">
-        <v>338</v>
+        <v>347</v>
       </c>
       <c r="AN39" t="s" s="2">
         <v>76</v>
@@ -6404,10 +6468,10 @@
     </row>
     <row r="40" hidden="true">
       <c r="A40" t="s" s="2">
-        <v>339</v>
+        <v>348</v>
       </c>
       <c r="B40" t="s" s="2">
-        <v>339</v>
+        <v>348</v>
       </c>
       <c r="C40" s="2"/>
       <c r="D40" t="s" s="2">
@@ -6430,13 +6494,13 @@
         <v>76</v>
       </c>
       <c r="K40" t="s" s="2">
-        <v>174</v>
+        <v>182</v>
       </c>
       <c r="L40" t="s" s="2">
-        <v>175</v>
+        <v>183</v>
       </c>
       <c r="M40" t="s" s="2">
-        <v>176</v>
+        <v>184</v>
       </c>
       <c r="N40" s="2"/>
       <c r="O40" s="2"/>
@@ -6487,7 +6551,7 @@
         <v>76</v>
       </c>
       <c r="AF40" t="s" s="2">
-        <v>177</v>
+        <v>185</v>
       </c>
       <c r="AG40" t="s" s="2">
         <v>77</v>
@@ -6508,7 +6572,7 @@
         <v>76</v>
       </c>
       <c r="AM40" t="s" s="2">
-        <v>178</v>
+        <v>186</v>
       </c>
       <c r="AN40" t="s" s="2">
         <v>76</v>
@@ -6516,10 +6580,10 @@
     </row>
     <row r="41" hidden="true">
       <c r="A41" t="s" s="2">
-        <v>340</v>
+        <v>349</v>
       </c>
       <c r="B41" t="s" s="2">
-        <v>340</v>
+        <v>349</v>
       </c>
       <c r="C41" s="2"/>
       <c r="D41" t="s" s="2">
@@ -6548,7 +6612,7 @@
         <v>135</v>
       </c>
       <c r="M41" t="s" s="2">
-        <v>180</v>
+        <v>188</v>
       </c>
       <c r="N41" t="s" s="2">
         <v>137</v>
@@ -6589,19 +6653,19 @@
         <v>76</v>
       </c>
       <c r="AB41" t="s" s="2">
-        <v>181</v>
+        <v>138</v>
       </c>
       <c r="AC41" t="s" s="2">
-        <v>182</v>
+        <v>139</v>
       </c>
       <c r="AD41" t="s" s="2">
         <v>76</v>
       </c>
       <c r="AE41" t="s" s="2">
-        <v>183</v>
+        <v>140</v>
       </c>
       <c r="AF41" t="s" s="2">
-        <v>184</v>
+        <v>189</v>
       </c>
       <c r="AG41" t="s" s="2">
         <v>77</v>
@@ -6613,7 +6677,7 @@
         <v>76</v>
       </c>
       <c r="AJ41" t="s" s="2">
-        <v>139</v>
+        <v>142</v>
       </c>
       <c r="AK41" t="s" s="2">
         <v>76</v>
@@ -6622,7 +6686,7 @@
         <v>76</v>
       </c>
       <c r="AM41" t="s" s="2">
-        <v>178</v>
+        <v>186</v>
       </c>
       <c r="AN41" t="s" s="2">
         <v>76</v>
@@ -6630,10 +6694,10 @@
     </row>
     <row r="42" hidden="true">
       <c r="A42" t="s" s="2">
-        <v>341</v>
+        <v>350</v>
       </c>
       <c r="B42" t="s" s="2">
-        <v>341</v>
+        <v>350</v>
       </c>
       <c r="C42" s="2"/>
       <c r="D42" t="s" s="2">
@@ -6656,16 +6720,16 @@
         <v>89</v>
       </c>
       <c r="K42" t="s" s="2">
-        <v>174</v>
+        <v>182</v>
       </c>
       <c r="L42" t="s" s="2">
-        <v>264</v>
+        <v>271</v>
       </c>
       <c r="M42" t="s" s="2">
-        <v>265</v>
+        <v>272</v>
       </c>
       <c r="N42" t="s" s="2">
-        <v>266</v>
+        <v>273</v>
       </c>
       <c r="O42" s="2"/>
       <c r="P42" t="s" s="2">
@@ -6715,7 +6779,7 @@
         <v>76</v>
       </c>
       <c r="AF42" t="s" s="2">
-        <v>267</v>
+        <v>274</v>
       </c>
       <c r="AG42" t="s" s="2">
         <v>77</v>
@@ -6724,7 +6788,7 @@
         <v>88</v>
       </c>
       <c r="AI42" t="s" s="2">
-        <v>268</v>
+        <v>275</v>
       </c>
       <c r="AJ42" t="s" s="2">
         <v>100</v>
@@ -6744,10 +6808,10 @@
     </row>
     <row r="43" hidden="true">
       <c r="A43" t="s" s="2">
-        <v>342</v>
+        <v>351</v>
       </c>
       <c r="B43" t="s" s="2">
-        <v>342</v>
+        <v>351</v>
       </c>
       <c r="C43" s="2"/>
       <c r="D43" t="s" s="2">
@@ -6773,13 +6837,13 @@
         <v>102</v>
       </c>
       <c r="L43" t="s" s="2">
-        <v>270</v>
+        <v>277</v>
       </c>
       <c r="M43" t="s" s="2">
-        <v>271</v>
+        <v>278</v>
       </c>
       <c r="N43" t="s" s="2">
-        <v>272</v>
+        <v>279</v>
       </c>
       <c r="O43" s="2"/>
       <c r="P43" t="s" s="2">
@@ -6805,13 +6869,13 @@
         <v>76</v>
       </c>
       <c r="X43" t="s" s="2">
-        <v>170</v>
+        <v>176</v>
       </c>
       <c r="Y43" t="s" s="2">
-        <v>273</v>
+        <v>280</v>
       </c>
       <c r="Z43" t="s" s="2">
-        <v>274</v>
+        <v>281</v>
       </c>
       <c r="AA43" t="s" s="2">
         <v>76</v>
@@ -6829,7 +6893,7 @@
         <v>76</v>
       </c>
       <c r="AF43" t="s" s="2">
-        <v>275</v>
+        <v>282</v>
       </c>
       <c r="AG43" t="s" s="2">
         <v>77</v>
@@ -6858,10 +6922,10 @@
     </row>
     <row r="44">
       <c r="A44" t="s" s="2">
-        <v>343</v>
+        <v>352</v>
       </c>
       <c r="B44" t="s" s="2">
-        <v>343</v>
+        <v>352</v>
       </c>
       <c r="C44" s="2"/>
       <c r="D44" t="s" s="2">
@@ -6884,16 +6948,16 @@
         <v>89</v>
       </c>
       <c r="K44" t="s" s="2">
-        <v>344</v>
+        <v>353</v>
       </c>
       <c r="L44" t="s" s="2">
-        <v>278</v>
+        <v>285</v>
       </c>
       <c r="M44" t="s" s="2">
-        <v>279</v>
+        <v>286</v>
       </c>
       <c r="N44" t="s" s="2">
-        <v>280</v>
+        <v>287</v>
       </c>
       <c r="O44" s="2"/>
       <c r="P44" t="s" s="2">
@@ -6943,7 +7007,7 @@
         <v>76</v>
       </c>
       <c r="AF44" t="s" s="2">
-        <v>281</v>
+        <v>288</v>
       </c>
       <c r="AG44" t="s" s="2">
         <v>77</v>
@@ -6952,7 +7016,7 @@
         <v>88</v>
       </c>
       <c r="AI44" t="s" s="2">
-        <v>76</v>
+        <v>154</v>
       </c>
       <c r="AJ44" t="s" s="2">
         <v>100</v>
@@ -6961,10 +7025,10 @@
         <v>76</v>
       </c>
       <c r="AL44" t="s" s="2">
-        <v>76</v>
+        <v>156</v>
       </c>
       <c r="AM44" t="s" s="2">
-        <v>282</v>
+        <v>289</v>
       </c>
       <c r="AN44" t="s" s="2">
         <v>76</v>
@@ -6972,10 +7036,10 @@
     </row>
     <row r="45" hidden="true">
       <c r="A45" t="s" s="2">
-        <v>345</v>
+        <v>354</v>
       </c>
       <c r="B45" t="s" s="2">
-        <v>345</v>
+        <v>354</v>
       </c>
       <c r="C45" s="2"/>
       <c r="D45" t="s" s="2">
@@ -6998,16 +7062,16 @@
         <v>89</v>
       </c>
       <c r="K45" t="s" s="2">
-        <v>174</v>
+        <v>182</v>
       </c>
       <c r="L45" t="s" s="2">
-        <v>346</v>
+        <v>355</v>
       </c>
       <c r="M45" t="s" s="2">
-        <v>347</v>
+        <v>356</v>
       </c>
       <c r="N45" t="s" s="2">
-        <v>348</v>
+        <v>357</v>
       </c>
       <c r="O45" s="2"/>
       <c r="P45" t="s" s="2">
@@ -7057,7 +7121,7 @@
         <v>76</v>
       </c>
       <c r="AF45" t="s" s="2">
-        <v>349</v>
+        <v>358</v>
       </c>
       <c r="AG45" t="s" s="2">
         <v>77</v>
@@ -7086,10 +7150,10 @@
     </row>
     <row r="46" hidden="true">
       <c r="A46" t="s" s="2">
-        <v>350</v>
+        <v>359</v>
       </c>
       <c r="B46" t="s" s="2">
-        <v>350</v>
+        <v>359</v>
       </c>
       <c r="C46" s="2"/>
       <c r="D46" t="s" s="2">
@@ -7112,16 +7176,16 @@
         <v>89</v>
       </c>
       <c r="K46" t="s" s="2">
-        <v>174</v>
+        <v>182</v>
       </c>
       <c r="L46" t="s" s="2">
-        <v>346</v>
+        <v>355</v>
       </c>
       <c r="M46" t="s" s="2">
-        <v>347</v>
+        <v>356</v>
       </c>
       <c r="N46" t="s" s="2">
-        <v>348</v>
+        <v>357</v>
       </c>
       <c r="O46" s="2"/>
       <c r="P46" t="s" s="2">
@@ -7171,7 +7235,7 @@
         <v>76</v>
       </c>
       <c r="AF46" t="s" s="2">
-        <v>349</v>
+        <v>358</v>
       </c>
       <c r="AG46" t="s" s="2">
         <v>77</v>
@@ -7200,10 +7264,10 @@
     </row>
     <row r="47">
       <c r="A47" t="s" s="2">
-        <v>351</v>
+        <v>360</v>
       </c>
       <c r="B47" t="s" s="2">
-        <v>351</v>
+        <v>360</v>
       </c>
       <c r="C47" s="2"/>
       <c r="D47" t="s" s="2">
@@ -7226,16 +7290,16 @@
         <v>89</v>
       </c>
       <c r="K47" t="s" s="2">
-        <v>352</v>
+        <v>361</v>
       </c>
       <c r="L47" t="s" s="2">
-        <v>353</v>
+        <v>362</v>
       </c>
       <c r="M47" t="s" s="2">
-        <v>354</v>
+        <v>363</v>
       </c>
       <c r="N47" t="s" s="2">
-        <v>355</v>
+        <v>364</v>
       </c>
       <c r="O47" s="2"/>
       <c r="P47" t="s" s="2">
@@ -7285,7 +7349,7 @@
         <v>76</v>
       </c>
       <c r="AF47" t="s" s="2">
-        <v>351</v>
+        <v>360</v>
       </c>
       <c r="AG47" t="s" s="2">
         <v>77</v>
@@ -7300,28 +7364,28 @@
         <v>100</v>
       </c>
       <c r="AK47" t="s" s="2">
-        <v>356</v>
+        <v>365</v>
       </c>
       <c r="AL47" t="s" s="2">
-        <v>357</v>
+        <v>366</v>
       </c>
       <c r="AM47" t="s" s="2">
-        <v>358</v>
+        <v>367</v>
       </c>
       <c r="AN47" t="s" s="2">
-        <v>359</v>
+        <v>368</v>
       </c>
     </row>
     <row r="48" hidden="true">
       <c r="A48" t="s" s="2">
-        <v>360</v>
+        <v>369</v>
       </c>
       <c r="B48" t="s" s="2">
-        <v>360</v>
+        <v>369</v>
       </c>
       <c r="C48" s="2"/>
       <c r="D48" t="s" s="2">
-        <v>361</v>
+        <v>370</v>
       </c>
       <c r="E48" s="2"/>
       <c r="F48" t="s" s="2">
@@ -7340,16 +7404,16 @@
         <v>89</v>
       </c>
       <c r="K48" t="s" s="2">
-        <v>362</v>
+        <v>371</v>
       </c>
       <c r="L48" t="s" s="2">
-        <v>363</v>
+        <v>372</v>
       </c>
       <c r="M48" t="s" s="2">
-        <v>364</v>
+        <v>373</v>
       </c>
       <c r="N48" t="s" s="2">
-        <v>365</v>
+        <v>374</v>
       </c>
       <c r="O48" s="2"/>
       <c r="P48" t="s" s="2">
@@ -7399,7 +7463,7 @@
         <v>76</v>
       </c>
       <c r="AF48" t="s" s="2">
-        <v>360</v>
+        <v>369</v>
       </c>
       <c r="AG48" t="s" s="2">
         <v>77</v>
@@ -7408,34 +7472,34 @@
         <v>78</v>
       </c>
       <c r="AI48" t="s" s="2">
-        <v>76</v>
+        <v>154</v>
       </c>
       <c r="AJ48" t="s" s="2">
-        <v>100</v>
+        <v>264</v>
       </c>
       <c r="AK48" t="s" s="2">
-        <v>366</v>
+        <v>375</v>
       </c>
       <c r="AL48" t="s" s="2">
-        <v>367</v>
+        <v>376</v>
       </c>
       <c r="AM48" t="s" s="2">
-        <v>76</v>
+        <v>377</v>
       </c>
       <c r="AN48" t="s" s="2">
-        <v>368</v>
+        <v>378</v>
       </c>
     </row>
     <row r="49" hidden="true">
       <c r="A49" t="s" s="2">
-        <v>369</v>
+        <v>379</v>
       </c>
       <c r="B49" t="s" s="2">
-        <v>369</v>
+        <v>379</v>
       </c>
       <c r="C49" s="2"/>
       <c r="D49" t="s" s="2">
-        <v>370</v>
+        <v>380</v>
       </c>
       <c r="E49" s="2"/>
       <c r="F49" t="s" s="2">
@@ -7454,15 +7518,17 @@
         <v>89</v>
       </c>
       <c r="K49" t="s" s="2">
-        <v>371</v>
+        <v>381</v>
       </c>
       <c r="L49" t="s" s="2">
-        <v>372</v>
+        <v>382</v>
       </c>
       <c r="M49" t="s" s="2">
-        <v>373</v>
-      </c>
-      <c r="N49" s="2"/>
+        <v>383</v>
+      </c>
+      <c r="N49" t="s" s="2">
+        <v>384</v>
+      </c>
       <c r="O49" s="2"/>
       <c r="P49" t="s" s="2">
         <v>76</v>
@@ -7511,7 +7577,7 @@
         <v>76</v>
       </c>
       <c r="AF49" t="s" s="2">
-        <v>369</v>
+        <v>379</v>
       </c>
       <c r="AG49" t="s" s="2">
         <v>77</v>
@@ -7520,30 +7586,30 @@
         <v>78</v>
       </c>
       <c r="AI49" t="s" s="2">
-        <v>76</v>
+        <v>154</v>
       </c>
       <c r="AJ49" t="s" s="2">
-        <v>100</v>
+        <v>264</v>
       </c>
       <c r="AK49" t="s" s="2">
-        <v>366</v>
+        <v>375</v>
       </c>
       <c r="AL49" t="s" s="2">
         <v>76</v>
       </c>
       <c r="AM49" t="s" s="2">
-        <v>76</v>
+        <v>377</v>
       </c>
       <c r="AN49" t="s" s="2">
-        <v>374</v>
+        <v>385</v>
       </c>
     </row>
     <row r="50" hidden="true">
       <c r="A50" t="s" s="2">
-        <v>375</v>
+        <v>386</v>
       </c>
       <c r="B50" t="s" s="2">
-        <v>375</v>
+        <v>386</v>
       </c>
       <c r="C50" s="2"/>
       <c r="D50" t="s" s="2">
@@ -7566,16 +7632,16 @@
         <v>89</v>
       </c>
       <c r="K50" t="s" s="2">
-        <v>376</v>
+        <v>387</v>
       </c>
       <c r="L50" t="s" s="2">
-        <v>377</v>
+        <v>388</v>
       </c>
       <c r="M50" t="s" s="2">
-        <v>378</v>
+        <v>389</v>
       </c>
       <c r="N50" t="s" s="2">
-        <v>379</v>
+        <v>390</v>
       </c>
       <c r="O50" s="2"/>
       <c r="P50" t="s" s="2">
@@ -7625,7 +7691,7 @@
         <v>76</v>
       </c>
       <c r="AF50" t="s" s="2">
-        <v>375</v>
+        <v>386</v>
       </c>
       <c r="AG50" t="s" s="2">
         <v>77</v>
@@ -7634,7 +7700,7 @@
         <v>88</v>
       </c>
       <c r="AI50" t="s" s="2">
-        <v>76</v>
+        <v>154</v>
       </c>
       <c r="AJ50" t="s" s="2">
         <v>100</v>
@@ -7643,10 +7709,10 @@
         <v>76</v>
       </c>
       <c r="AL50" t="s" s="2">
-        <v>380</v>
+        <v>391</v>
       </c>
       <c r="AM50" t="s" s="2">
-        <v>76</v>
+        <v>186</v>
       </c>
       <c r="AN50" t="s" s="2">
         <v>76</v>
@@ -7654,10 +7720,10 @@
     </row>
     <row r="51" hidden="true">
       <c r="A51" t="s" s="2">
-        <v>381</v>
+        <v>392</v>
       </c>
       <c r="B51" t="s" s="2">
-        <v>381</v>
+        <v>392</v>
       </c>
       <c r="C51" s="2"/>
       <c r="D51" t="s" s="2">
@@ -7680,13 +7746,13 @@
         <v>76</v>
       </c>
       <c r="K51" t="s" s="2">
-        <v>382</v>
+        <v>393</v>
       </c>
       <c r="L51" t="s" s="2">
-        <v>383</v>
+        <v>394</v>
       </c>
       <c r="M51" t="s" s="2">
-        <v>384</v>
+        <v>395</v>
       </c>
       <c r="N51" s="2"/>
       <c r="O51" s="2"/>
@@ -7737,7 +7803,7 @@
         <v>76</v>
       </c>
       <c r="AF51" t="s" s="2">
-        <v>381</v>
+        <v>392</v>
       </c>
       <c r="AG51" t="s" s="2">
         <v>77</v>
@@ -7746,7 +7812,7 @@
         <v>78</v>
       </c>
       <c r="AI51" t="s" s="2">
-        <v>76</v>
+        <v>154</v>
       </c>
       <c r="AJ51" t="s" s="2">
         <v>100</v>
@@ -7758,7 +7824,7 @@
         <v>76</v>
       </c>
       <c r="AM51" t="s" s="2">
-        <v>76</v>
+        <v>186</v>
       </c>
       <c r="AN51" t="s" s="2">
         <v>76</v>
@@ -7766,10 +7832,10 @@
     </row>
     <row r="52" hidden="true">
       <c r="A52" t="s" s="2">
-        <v>385</v>
+        <v>396</v>
       </c>
       <c r="B52" t="s" s="2">
-        <v>385</v>
+        <v>396</v>
       </c>
       <c r="C52" s="2"/>
       <c r="D52" t="s" s="2">
@@ -7792,13 +7858,13 @@
         <v>76</v>
       </c>
       <c r="K52" t="s" s="2">
-        <v>174</v>
+        <v>182</v>
       </c>
       <c r="L52" t="s" s="2">
-        <v>175</v>
+        <v>183</v>
       </c>
       <c r="M52" t="s" s="2">
-        <v>176</v>
+        <v>184</v>
       </c>
       <c r="N52" s="2"/>
       <c r="O52" s="2"/>
@@ -7849,7 +7915,7 @@
         <v>76</v>
       </c>
       <c r="AF52" t="s" s="2">
-        <v>177</v>
+        <v>185</v>
       </c>
       <c r="AG52" t="s" s="2">
         <v>77</v>
@@ -7870,7 +7936,7 @@
         <v>76</v>
       </c>
       <c r="AM52" t="s" s="2">
-        <v>178</v>
+        <v>186</v>
       </c>
       <c r="AN52" t="s" s="2">
         <v>76</v>
@@ -7878,10 +7944,10 @@
     </row>
     <row r="53" hidden="true">
       <c r="A53" t="s" s="2">
-        <v>386</v>
+        <v>397</v>
       </c>
       <c r="B53" t="s" s="2">
-        <v>386</v>
+        <v>397</v>
       </c>
       <c r="C53" s="2"/>
       <c r="D53" t="s" s="2">
@@ -7910,7 +7976,7 @@
         <v>135</v>
       </c>
       <c r="M53" t="s" s="2">
-        <v>180</v>
+        <v>188</v>
       </c>
       <c r="N53" t="s" s="2">
         <v>137</v>
@@ -7951,19 +8017,19 @@
         <v>76</v>
       </c>
       <c r="AB53" t="s" s="2">
-        <v>76</v>
+        <v>138</v>
       </c>
       <c r="AC53" t="s" s="2">
-        <v>76</v>
+        <v>139</v>
       </c>
       <c r="AD53" t="s" s="2">
         <v>76</v>
       </c>
       <c r="AE53" t="s" s="2">
-        <v>76</v>
+        <v>140</v>
       </c>
       <c r="AF53" t="s" s="2">
-        <v>184</v>
+        <v>189</v>
       </c>
       <c r="AG53" t="s" s="2">
         <v>77</v>
@@ -7975,7 +8041,7 @@
         <v>76</v>
       </c>
       <c r="AJ53" t="s" s="2">
-        <v>139</v>
+        <v>142</v>
       </c>
       <c r="AK53" t="s" s="2">
         <v>76</v>
@@ -7984,7 +8050,7 @@
         <v>76</v>
       </c>
       <c r="AM53" t="s" s="2">
-        <v>178</v>
+        <v>186</v>
       </c>
       <c r="AN53" t="s" s="2">
         <v>76</v>
@@ -7992,14 +8058,14 @@
     </row>
     <row r="54" hidden="true">
       <c r="A54" t="s" s="2">
-        <v>387</v>
+        <v>398</v>
       </c>
       <c r="B54" t="s" s="2">
-        <v>387</v>
+        <v>398</v>
       </c>
       <c r="C54" s="2"/>
       <c r="D54" t="s" s="2">
-        <v>388</v>
+        <v>399</v>
       </c>
       <c r="E54" s="2"/>
       <c r="F54" t="s" s="2">
@@ -8021,16 +8087,16 @@
         <v>134</v>
       </c>
       <c r="L54" t="s" s="2">
-        <v>389</v>
+        <v>400</v>
       </c>
       <c r="M54" t="s" s="2">
-        <v>390</v>
+        <v>401</v>
       </c>
       <c r="N54" t="s" s="2">
         <v>137</v>
       </c>
       <c r="O54" t="s" s="2">
-        <v>143</v>
+        <v>146</v>
       </c>
       <c r="P54" t="s" s="2">
         <v>76</v>
@@ -8079,7 +8145,7 @@
         <v>76</v>
       </c>
       <c r="AF54" t="s" s="2">
-        <v>391</v>
+        <v>402</v>
       </c>
       <c r="AG54" t="s" s="2">
         <v>77</v>
@@ -8091,7 +8157,7 @@
         <v>76</v>
       </c>
       <c r="AJ54" t="s" s="2">
-        <v>139</v>
+        <v>142</v>
       </c>
       <c r="AK54" t="s" s="2">
         <v>76</v>
@@ -8108,10 +8174,10 @@
     </row>
     <row r="55" hidden="true">
       <c r="A55" t="s" s="2">
-        <v>392</v>
+        <v>403</v>
       </c>
       <c r="B55" t="s" s="2">
-        <v>392</v>
+        <v>403</v>
       </c>
       <c r="C55" s="2"/>
       <c r="D55" t="s" s="2">
@@ -8137,12 +8203,14 @@
         <v>102</v>
       </c>
       <c r="L55" t="s" s="2">
-        <v>393</v>
+        <v>404</v>
       </c>
       <c r="M55" t="s" s="2">
-        <v>394</v>
-      </c>
-      <c r="N55" s="2"/>
+        <v>405</v>
+      </c>
+      <c r="N55" t="s" s="2">
+        <v>406</v>
+      </c>
       <c r="O55" s="2"/>
       <c r="P55" t="s" s="2">
         <v>76</v>
@@ -8191,7 +8259,7 @@
         <v>76</v>
       </c>
       <c r="AF55" t="s" s="2">
-        <v>392</v>
+        <v>403</v>
       </c>
       <c r="AG55" t="s" s="2">
         <v>77</v>
@@ -8200,7 +8268,7 @@
         <v>88</v>
       </c>
       <c r="AI55" t="s" s="2">
-        <v>395</v>
+        <v>407</v>
       </c>
       <c r="AJ55" t="s" s="2">
         <v>100</v>
@@ -8220,10 +8288,10 @@
     </row>
     <row r="56" hidden="true">
       <c r="A56" t="s" s="2">
-        <v>396</v>
+        <v>408</v>
       </c>
       <c r="B56" t="s" s="2">
-        <v>396</v>
+        <v>408</v>
       </c>
       <c r="C56" s="2"/>
       <c r="D56" t="s" s="2">
@@ -8249,13 +8317,13 @@
         <v>102</v>
       </c>
       <c r="L56" t="s" s="2">
-        <v>397</v>
+        <v>409</v>
       </c>
       <c r="M56" t="s" s="2">
-        <v>384</v>
+        <v>395</v>
       </c>
       <c r="N56" t="s" s="2">
-        <v>398</v>
+        <v>410</v>
       </c>
       <c r="O56" s="2"/>
       <c r="P56" t="s" s="2">
@@ -8305,7 +8373,7 @@
         <v>76</v>
       </c>
       <c r="AF56" t="s" s="2">
-        <v>396</v>
+        <v>408</v>
       </c>
       <c r="AG56" t="s" s="2">
         <v>77</v>
@@ -8314,7 +8382,7 @@
         <v>88</v>
       </c>
       <c r="AI56" t="s" s="2">
-        <v>395</v>
+        <v>407</v>
       </c>
       <c r="AJ56" t="s" s="2">
         <v>100</v>
@@ -8334,10 +8402,10 @@
     </row>
     <row r="57">
       <c r="A57" t="s" s="2">
-        <v>399</v>
+        <v>411</v>
       </c>
       <c r="B57" t="s" s="2">
-        <v>399</v>
+        <v>411</v>
       </c>
       <c r="C57" s="2"/>
       <c r="D57" t="s" s="2">
@@ -8360,19 +8428,19 @@
         <v>89</v>
       </c>
       <c r="K57" t="s" s="2">
-        <v>167</v>
+        <v>172</v>
       </c>
       <c r="L57" t="s" s="2">
-        <v>400</v>
+        <v>412</v>
       </c>
       <c r="M57" t="s" s="2">
-        <v>401</v>
+        <v>413</v>
       </c>
       <c r="N57" t="s" s="2">
-        <v>402</v>
+        <v>414</v>
       </c>
       <c r="O57" t="s" s="2">
-        <v>403</v>
+        <v>415</v>
       </c>
       <c r="P57" t="s" s="2">
         <v>76</v>
@@ -8397,11 +8465,11 @@
         <v>76</v>
       </c>
       <c r="X57" t="s" s="2">
-        <v>159</v>
+        <v>164</v>
       </c>
       <c r="Y57" s="2"/>
       <c r="Z57" t="s" s="2">
-        <v>404</v>
+        <v>416</v>
       </c>
       <c r="AA57" t="s" s="2">
         <v>76</v>
@@ -8419,7 +8487,7 @@
         <v>76</v>
       </c>
       <c r="AF57" t="s" s="2">
-        <v>399</v>
+        <v>411</v>
       </c>
       <c r="AG57" t="s" s="2">
         <v>77</v>
@@ -8428,7 +8496,7 @@
         <v>88</v>
       </c>
       <c r="AI57" t="s" s="2">
-        <v>395</v>
+        <v>417</v>
       </c>
       <c r="AJ57" t="s" s="2">
         <v>100</v>
@@ -8437,10 +8505,10 @@
         <v>76</v>
       </c>
       <c r="AL57" t="s" s="2">
-        <v>76</v>
+        <v>179</v>
       </c>
       <c r="AM57" t="s" s="2">
-        <v>76</v>
+        <v>180</v>
       </c>
       <c r="AN57" t="s" s="2">
         <v>76</v>
@@ -8448,10 +8516,10 @@
     </row>
     <row r="58" hidden="true">
       <c r="A58" t="s" s="2">
-        <v>405</v>
+        <v>418</v>
       </c>
       <c r="B58" t="s" s="2">
-        <v>405</v>
+        <v>418</v>
       </c>
       <c r="C58" s="2"/>
       <c r="D58" t="s" s="2">
@@ -8474,13 +8542,13 @@
         <v>89</v>
       </c>
       <c r="K58" t="s" s="2">
-        <v>382</v>
+        <v>393</v>
       </c>
       <c r="L58" t="s" s="2">
-        <v>406</v>
+        <v>419</v>
       </c>
       <c r="M58" t="s" s="2">
-        <v>407</v>
+        <v>420</v>
       </c>
       <c r="N58" s="2"/>
       <c r="O58" s="2"/>
@@ -8531,7 +8599,7 @@
         <v>76</v>
       </c>
       <c r="AF58" t="s" s="2">
-        <v>405</v>
+        <v>418</v>
       </c>
       <c r="AG58" t="s" s="2">
         <v>77</v>
@@ -8540,7 +8608,7 @@
         <v>78</v>
       </c>
       <c r="AI58" t="s" s="2">
-        <v>76</v>
+        <v>154</v>
       </c>
       <c r="AJ58" t="s" s="2">
         <v>100</v>
@@ -8552,7 +8620,7 @@
         <v>76</v>
       </c>
       <c r="AM58" t="s" s="2">
-        <v>76</v>
+        <v>186</v>
       </c>
       <c r="AN58" t="s" s="2">
         <v>76</v>
@@ -8560,10 +8628,10 @@
     </row>
     <row r="59" hidden="true">
       <c r="A59" t="s" s="2">
-        <v>408</v>
+        <v>421</v>
       </c>
       <c r="B59" t="s" s="2">
-        <v>408</v>
+        <v>421</v>
       </c>
       <c r="C59" s="2"/>
       <c r="D59" t="s" s="2">
@@ -8586,13 +8654,13 @@
         <v>76</v>
       </c>
       <c r="K59" t="s" s="2">
-        <v>174</v>
+        <v>182</v>
       </c>
       <c r="L59" t="s" s="2">
-        <v>175</v>
+        <v>183</v>
       </c>
       <c r="M59" t="s" s="2">
-        <v>176</v>
+        <v>184</v>
       </c>
       <c r="N59" s="2"/>
       <c r="O59" s="2"/>
@@ -8643,7 +8711,7 @@
         <v>76</v>
       </c>
       <c r="AF59" t="s" s="2">
-        <v>177</v>
+        <v>185</v>
       </c>
       <c r="AG59" t="s" s="2">
         <v>77</v>
@@ -8664,7 +8732,7 @@
         <v>76</v>
       </c>
       <c r="AM59" t="s" s="2">
-        <v>178</v>
+        <v>186</v>
       </c>
       <c r="AN59" t="s" s="2">
         <v>76</v>
@@ -8672,10 +8740,10 @@
     </row>
     <row r="60" hidden="true">
       <c r="A60" t="s" s="2">
-        <v>409</v>
+        <v>422</v>
       </c>
       <c r="B60" t="s" s="2">
-        <v>409</v>
+        <v>422</v>
       </c>
       <c r="C60" s="2"/>
       <c r="D60" t="s" s="2">
@@ -8704,7 +8772,7 @@
         <v>135</v>
       </c>
       <c r="M60" t="s" s="2">
-        <v>180</v>
+        <v>188</v>
       </c>
       <c r="N60" t="s" s="2">
         <v>137</v>
@@ -8745,19 +8813,19 @@
         <v>76</v>
       </c>
       <c r="AB60" t="s" s="2">
-        <v>76</v>
+        <v>138</v>
       </c>
       <c r="AC60" t="s" s="2">
-        <v>76</v>
+        <v>139</v>
       </c>
       <c r="AD60" t="s" s="2">
         <v>76</v>
       </c>
       <c r="AE60" t="s" s="2">
-        <v>76</v>
+        <v>140</v>
       </c>
       <c r="AF60" t="s" s="2">
-        <v>184</v>
+        <v>189</v>
       </c>
       <c r="AG60" t="s" s="2">
         <v>77</v>
@@ -8769,7 +8837,7 @@
         <v>76</v>
       </c>
       <c r="AJ60" t="s" s="2">
-        <v>139</v>
+        <v>142</v>
       </c>
       <c r="AK60" t="s" s="2">
         <v>76</v>
@@ -8778,7 +8846,7 @@
         <v>76</v>
       </c>
       <c r="AM60" t="s" s="2">
-        <v>178</v>
+        <v>186</v>
       </c>
       <c r="AN60" t="s" s="2">
         <v>76</v>
@@ -8786,14 +8854,14 @@
     </row>
     <row r="61" hidden="true">
       <c r="A61" t="s" s="2">
-        <v>410</v>
+        <v>423</v>
       </c>
       <c r="B61" t="s" s="2">
-        <v>410</v>
+        <v>423</v>
       </c>
       <c r="C61" s="2"/>
       <c r="D61" t="s" s="2">
-        <v>388</v>
+        <v>399</v>
       </c>
       <c r="E61" s="2"/>
       <c r="F61" t="s" s="2">
@@ -8815,16 +8883,16 @@
         <v>134</v>
       </c>
       <c r="L61" t="s" s="2">
-        <v>389</v>
+        <v>400</v>
       </c>
       <c r="M61" t="s" s="2">
-        <v>390</v>
+        <v>401</v>
       </c>
       <c r="N61" t="s" s="2">
         <v>137</v>
       </c>
       <c r="O61" t="s" s="2">
-        <v>143</v>
+        <v>146</v>
       </c>
       <c r="P61" t="s" s="2">
         <v>76</v>
@@ -8873,7 +8941,7 @@
         <v>76</v>
       </c>
       <c r="AF61" t="s" s="2">
-        <v>391</v>
+        <v>402</v>
       </c>
       <c r="AG61" t="s" s="2">
         <v>77</v>
@@ -8885,7 +8953,7 @@
         <v>76</v>
       </c>
       <c r="AJ61" t="s" s="2">
-        <v>139</v>
+        <v>142</v>
       </c>
       <c r="AK61" t="s" s="2">
         <v>76</v>
@@ -8902,10 +8970,10 @@
     </row>
     <row r="62" hidden="true">
       <c r="A62" t="s" s="2">
-        <v>411</v>
+        <v>424</v>
       </c>
       <c r="B62" t="s" s="2">
-        <v>411</v>
+        <v>424</v>
       </c>
       <c r="C62" s="2"/>
       <c r="D62" t="s" s="2">
@@ -8928,13 +8996,13 @@
         <v>89</v>
       </c>
       <c r="K62" t="s" s="2">
-        <v>229</v>
+        <v>235</v>
       </c>
       <c r="L62" t="s" s="2">
-        <v>412</v>
+        <v>425</v>
       </c>
       <c r="M62" t="s" s="2">
-        <v>413</v>
+        <v>426</v>
       </c>
       <c r="N62" s="2"/>
       <c r="O62" s="2"/>
@@ -8985,7 +9053,7 @@
         <v>76</v>
       </c>
       <c r="AF62" t="s" s="2">
-        <v>411</v>
+        <v>424</v>
       </c>
       <c r="AG62" t="s" s="2">
         <v>88</v>
@@ -9014,10 +9082,10 @@
     </row>
     <row r="63" hidden="true">
       <c r="A63" t="s" s="2">
-        <v>414</v>
+        <v>427</v>
       </c>
       <c r="B63" t="s" s="2">
-        <v>414</v>
+        <v>427</v>
       </c>
       <c r="C63" s="2"/>
       <c r="D63" t="s" s="2">
@@ -9040,15 +9108,17 @@
         <v>76</v>
       </c>
       <c r="K63" t="s" s="2">
-        <v>415</v>
+        <v>428</v>
       </c>
       <c r="L63" t="s" s="2">
-        <v>416</v>
+        <v>429</v>
       </c>
       <c r="M63" t="s" s="2">
-        <v>417</v>
-      </c>
-      <c r="N63" s="2"/>
+        <v>430</v>
+      </c>
+      <c r="N63" t="s" s="2">
+        <v>384</v>
+      </c>
       <c r="O63" s="2"/>
       <c r="P63" t="s" s="2">
         <v>76</v>
@@ -9097,7 +9167,7 @@
         <v>76</v>
       </c>
       <c r="AF63" t="s" s="2">
-        <v>414</v>
+        <v>427</v>
       </c>
       <c r="AG63" t="s" s="2">
         <v>77</v>
@@ -9106,10 +9176,10 @@
         <v>88</v>
       </c>
       <c r="AI63" t="s" s="2">
-        <v>76</v>
+        <v>154</v>
       </c>
       <c r="AJ63" t="s" s="2">
-        <v>100</v>
+        <v>264</v>
       </c>
       <c r="AK63" t="s" s="2">
         <v>76</v>
@@ -9118,7 +9188,7 @@
         <v>76</v>
       </c>
       <c r="AM63" t="s" s="2">
-        <v>76</v>
+        <v>377</v>
       </c>
       <c r="AN63" t="s" s="2">
         <v>76</v>
@@ -9126,10 +9196,10 @@
     </row>
     <row r="64" hidden="true">
       <c r="A64" t="s" s="2">
-        <v>418</v>
+        <v>431</v>
       </c>
       <c r="B64" t="s" s="2">
-        <v>418</v>
+        <v>431</v>
       </c>
       <c r="C64" s="2"/>
       <c r="D64" t="s" s="2">
@@ -9152,13 +9222,13 @@
         <v>76</v>
       </c>
       <c r="K64" t="s" s="2">
-        <v>352</v>
+        <v>361</v>
       </c>
       <c r="L64" t="s" s="2">
-        <v>419</v>
+        <v>432</v>
       </c>
       <c r="M64" t="s" s="2">
-        <v>420</v>
+        <v>433</v>
       </c>
       <c r="N64" s="2"/>
       <c r="O64" s="2"/>
@@ -9209,7 +9279,7 @@
         <v>76</v>
       </c>
       <c r="AF64" t="s" s="2">
-        <v>418</v>
+        <v>431</v>
       </c>
       <c r="AG64" t="s" s="2">
         <v>77</v>
@@ -9238,10 +9308,10 @@
     </row>
     <row r="65" hidden="true">
       <c r="A65" t="s" s="2">
-        <v>421</v>
+        <v>434</v>
       </c>
       <c r="B65" t="s" s="2">
-        <v>421</v>
+        <v>434</v>
       </c>
       <c r="C65" s="2"/>
       <c r="D65" t="s" s="2">
@@ -9264,13 +9334,13 @@
         <v>89</v>
       </c>
       <c r="K65" t="s" s="2">
-        <v>382</v>
+        <v>393</v>
       </c>
       <c r="L65" t="s" s="2">
-        <v>422</v>
+        <v>435</v>
       </c>
       <c r="M65" t="s" s="2">
-        <v>423</v>
+        <v>436</v>
       </c>
       <c r="N65" s="2"/>
       <c r="O65" s="2"/>
@@ -9321,7 +9391,7 @@
         <v>76</v>
       </c>
       <c r="AF65" t="s" s="2">
-        <v>421</v>
+        <v>434</v>
       </c>
       <c r="AG65" t="s" s="2">
         <v>77</v>
@@ -9330,7 +9400,7 @@
         <v>88</v>
       </c>
       <c r="AI65" t="s" s="2">
-        <v>76</v>
+        <v>154</v>
       </c>
       <c r="AJ65" t="s" s="2">
         <v>100</v>
@@ -9342,7 +9412,7 @@
         <v>76</v>
       </c>
       <c r="AM65" t="s" s="2">
-        <v>76</v>
+        <v>186</v>
       </c>
       <c r="AN65" t="s" s="2">
         <v>76</v>
@@ -9350,10 +9420,10 @@
     </row>
     <row r="66" hidden="true">
       <c r="A66" t="s" s="2">
-        <v>424</v>
+        <v>437</v>
       </c>
       <c r="B66" t="s" s="2">
-        <v>424</v>
+        <v>437</v>
       </c>
       <c r="C66" s="2"/>
       <c r="D66" t="s" s="2">
@@ -9376,13 +9446,13 @@
         <v>76</v>
       </c>
       <c r="K66" t="s" s="2">
-        <v>174</v>
+        <v>182</v>
       </c>
       <c r="L66" t="s" s="2">
-        <v>175</v>
+        <v>183</v>
       </c>
       <c r="M66" t="s" s="2">
-        <v>176</v>
+        <v>184</v>
       </c>
       <c r="N66" s="2"/>
       <c r="O66" s="2"/>
@@ -9433,7 +9503,7 @@
         <v>76</v>
       </c>
       <c r="AF66" t="s" s="2">
-        <v>177</v>
+        <v>185</v>
       </c>
       <c r="AG66" t="s" s="2">
         <v>77</v>
@@ -9454,7 +9524,7 @@
         <v>76</v>
       </c>
       <c r="AM66" t="s" s="2">
-        <v>178</v>
+        <v>186</v>
       </c>
       <c r="AN66" t="s" s="2">
         <v>76</v>
@@ -9462,10 +9532,10 @@
     </row>
     <row r="67" hidden="true">
       <c r="A67" t="s" s="2">
-        <v>425</v>
+        <v>438</v>
       </c>
       <c r="B67" t="s" s="2">
-        <v>425</v>
+        <v>438</v>
       </c>
       <c r="C67" s="2"/>
       <c r="D67" t="s" s="2">
@@ -9494,7 +9564,7 @@
         <v>135</v>
       </c>
       <c r="M67" t="s" s="2">
-        <v>180</v>
+        <v>188</v>
       </c>
       <c r="N67" t="s" s="2">
         <v>137</v>
@@ -9535,19 +9605,19 @@
         <v>76</v>
       </c>
       <c r="AB67" t="s" s="2">
-        <v>76</v>
+        <v>138</v>
       </c>
       <c r="AC67" t="s" s="2">
-        <v>76</v>
+        <v>139</v>
       </c>
       <c r="AD67" t="s" s="2">
         <v>76</v>
       </c>
       <c r="AE67" t="s" s="2">
-        <v>76</v>
+        <v>140</v>
       </c>
       <c r="AF67" t="s" s="2">
-        <v>184</v>
+        <v>189</v>
       </c>
       <c r="AG67" t="s" s="2">
         <v>77</v>
@@ -9559,7 +9629,7 @@
         <v>76</v>
       </c>
       <c r="AJ67" t="s" s="2">
-        <v>139</v>
+        <v>142</v>
       </c>
       <c r="AK67" t="s" s="2">
         <v>76</v>
@@ -9568,7 +9638,7 @@
         <v>76</v>
       </c>
       <c r="AM67" t="s" s="2">
-        <v>178</v>
+        <v>186</v>
       </c>
       <c r="AN67" t="s" s="2">
         <v>76</v>
@@ -9576,14 +9646,14 @@
     </row>
     <row r="68" hidden="true">
       <c r="A68" t="s" s="2">
-        <v>426</v>
+        <v>439</v>
       </c>
       <c r="B68" t="s" s="2">
-        <v>426</v>
+        <v>439</v>
       </c>
       <c r="C68" s="2"/>
       <c r="D68" t="s" s="2">
-        <v>388</v>
+        <v>399</v>
       </c>
       <c r="E68" s="2"/>
       <c r="F68" t="s" s="2">
@@ -9605,16 +9675,16 @@
         <v>134</v>
       </c>
       <c r="L68" t="s" s="2">
-        <v>389</v>
+        <v>400</v>
       </c>
       <c r="M68" t="s" s="2">
-        <v>390</v>
+        <v>401</v>
       </c>
       <c r="N68" t="s" s="2">
         <v>137</v>
       </c>
       <c r="O68" t="s" s="2">
-        <v>143</v>
+        <v>146</v>
       </c>
       <c r="P68" t="s" s="2">
         <v>76</v>
@@ -9663,7 +9733,7 @@
         <v>76</v>
       </c>
       <c r="AF68" t="s" s="2">
-        <v>391</v>
+        <v>402</v>
       </c>
       <c r="AG68" t="s" s="2">
         <v>77</v>
@@ -9675,7 +9745,7 @@
         <v>76</v>
       </c>
       <c r="AJ68" t="s" s="2">
-        <v>139</v>
+        <v>142</v>
       </c>
       <c r="AK68" t="s" s="2">
         <v>76</v>
@@ -9692,10 +9762,10 @@
     </row>
     <row r="69" hidden="true">
       <c r="A69" t="s" s="2">
-        <v>427</v>
+        <v>440</v>
       </c>
       <c r="B69" t="s" s="2">
-        <v>427</v>
+        <v>440</v>
       </c>
       <c r="C69" s="2"/>
       <c r="D69" t="s" s="2">
@@ -9721,10 +9791,10 @@
         <v>108</v>
       </c>
       <c r="L69" t="s" s="2">
-        <v>428</v>
+        <v>441</v>
       </c>
       <c r="M69" t="s" s="2">
-        <v>429</v>
+        <v>442</v>
       </c>
       <c r="N69" s="2"/>
       <c r="O69" s="2"/>
@@ -9751,13 +9821,13 @@
         <v>76</v>
       </c>
       <c r="X69" t="s" s="2">
-        <v>159</v>
+        <v>164</v>
       </c>
       <c r="Y69" t="s" s="2">
-        <v>430</v>
+        <v>443</v>
       </c>
       <c r="Z69" t="s" s="2">
-        <v>431</v>
+        <v>444</v>
       </c>
       <c r="AA69" t="s" s="2">
         <v>76</v>
@@ -9775,7 +9845,7 @@
         <v>76</v>
       </c>
       <c r="AF69" t="s" s="2">
-        <v>427</v>
+        <v>440</v>
       </c>
       <c r="AG69" t="s" s="2">
         <v>77</v>
@@ -9804,10 +9874,10 @@
     </row>
     <row r="70" hidden="true">
       <c r="A70" t="s" s="2">
-        <v>432</v>
+        <v>445</v>
       </c>
       <c r="B70" t="s" s="2">
-        <v>432</v>
+        <v>445</v>
       </c>
       <c r="C70" s="2"/>
       <c r="D70" t="s" s="2">
@@ -9830,15 +9900,17 @@
         <v>89</v>
       </c>
       <c r="K70" t="s" s="2">
-        <v>325</v>
+        <v>332</v>
       </c>
       <c r="L70" t="s" s="2">
-        <v>433</v>
+        <v>446</v>
       </c>
       <c r="M70" t="s" s="2">
-        <v>434</v>
-      </c>
-      <c r="N70" s="2"/>
+        <v>447</v>
+      </c>
+      <c r="N70" t="s" s="2">
+        <v>335</v>
+      </c>
       <c r="O70" s="2"/>
       <c r="P70" t="s" s="2">
         <v>76</v>
@@ -9887,7 +9959,7 @@
         <v>76</v>
       </c>
       <c r="AF70" t="s" s="2">
-        <v>432</v>
+        <v>445</v>
       </c>
       <c r="AG70" t="s" s="2">
         <v>77</v>
@@ -9896,19 +9968,19 @@
         <v>88</v>
       </c>
       <c r="AI70" t="s" s="2">
-        <v>76</v>
+        <v>154</v>
       </c>
       <c r="AJ70" t="s" s="2">
-        <v>100</v>
+        <v>337</v>
       </c>
       <c r="AK70" t="s" s="2">
         <v>76</v>
       </c>
       <c r="AL70" t="s" s="2">
-        <v>76</v>
+        <v>448</v>
       </c>
       <c r="AM70" t="s" s="2">
-        <v>76</v>
+        <v>449</v>
       </c>
       <c r="AN70" t="s" s="2">
         <v>76</v>
@@ -9916,10 +9988,10 @@
     </row>
     <row r="71" hidden="true">
       <c r="A71" t="s" s="2">
-        <v>435</v>
+        <v>450</v>
       </c>
       <c r="B71" t="s" s="2">
-        <v>435</v>
+        <v>450</v>
       </c>
       <c r="C71" s="2"/>
       <c r="D71" t="s" s="2">
@@ -9942,13 +10014,13 @@
         <v>76</v>
       </c>
       <c r="K71" t="s" s="2">
-        <v>382</v>
+        <v>393</v>
       </c>
       <c r="L71" t="s" s="2">
-        <v>436</v>
+        <v>451</v>
       </c>
       <c r="M71" t="s" s="2">
-        <v>437</v>
+        <v>452</v>
       </c>
       <c r="N71" s="2"/>
       <c r="O71" s="2"/>
@@ -9956,7 +10028,7 @@
         <v>76</v>
       </c>
       <c r="Q71" t="s" s="2">
-        <v>438</v>
+        <v>453</v>
       </c>
       <c r="R71" t="s" s="2">
         <v>76</v>
@@ -10001,7 +10073,7 @@
         <v>76</v>
       </c>
       <c r="AF71" t="s" s="2">
-        <v>435</v>
+        <v>450</v>
       </c>
       <c r="AG71" t="s" s="2">
         <v>77</v>
@@ -10010,7 +10082,7 @@
         <v>78</v>
       </c>
       <c r="AI71" t="s" s="2">
-        <v>76</v>
+        <v>154</v>
       </c>
       <c r="AJ71" t="s" s="2">
         <v>100</v>
@@ -10022,7 +10094,7 @@
         <v>76</v>
       </c>
       <c r="AM71" t="s" s="2">
-        <v>76</v>
+        <v>186</v>
       </c>
       <c r="AN71" t="s" s="2">
         <v>76</v>
@@ -10030,10 +10102,10 @@
     </row>
     <row r="72" hidden="true">
       <c r="A72" t="s" s="2">
-        <v>439</v>
+        <v>454</v>
       </c>
       <c r="B72" t="s" s="2">
-        <v>439</v>
+        <v>454</v>
       </c>
       <c r="C72" s="2"/>
       <c r="D72" t="s" s="2">
@@ -10056,13 +10128,13 @@
         <v>76</v>
       </c>
       <c r="K72" t="s" s="2">
-        <v>174</v>
+        <v>182</v>
       </c>
       <c r="L72" t="s" s="2">
-        <v>175</v>
+        <v>183</v>
       </c>
       <c r="M72" t="s" s="2">
-        <v>176</v>
+        <v>184</v>
       </c>
       <c r="N72" s="2"/>
       <c r="O72" s="2"/>
@@ -10113,7 +10185,7 @@
         <v>76</v>
       </c>
       <c r="AF72" t="s" s="2">
-        <v>177</v>
+        <v>185</v>
       </c>
       <c r="AG72" t="s" s="2">
         <v>77</v>
@@ -10134,7 +10206,7 @@
         <v>76</v>
       </c>
       <c r="AM72" t="s" s="2">
-        <v>178</v>
+        <v>186</v>
       </c>
       <c r="AN72" t="s" s="2">
         <v>76</v>
@@ -10142,10 +10214,10 @@
     </row>
     <row r="73" hidden="true">
       <c r="A73" t="s" s="2">
-        <v>440</v>
+        <v>455</v>
       </c>
       <c r="B73" t="s" s="2">
-        <v>440</v>
+        <v>455</v>
       </c>
       <c r="C73" s="2"/>
       <c r="D73" t="s" s="2">
@@ -10174,7 +10246,7 @@
         <v>135</v>
       </c>
       <c r="M73" t="s" s="2">
-        <v>180</v>
+        <v>188</v>
       </c>
       <c r="N73" t="s" s="2">
         <v>137</v>
@@ -10215,19 +10287,19 @@
         <v>76</v>
       </c>
       <c r="AB73" t="s" s="2">
-        <v>76</v>
+        <v>138</v>
       </c>
       <c r="AC73" t="s" s="2">
-        <v>76</v>
+        <v>139</v>
       </c>
       <c r="AD73" t="s" s="2">
         <v>76</v>
       </c>
       <c r="AE73" t="s" s="2">
-        <v>76</v>
+        <v>140</v>
       </c>
       <c r="AF73" t="s" s="2">
-        <v>184</v>
+        <v>189</v>
       </c>
       <c r="AG73" t="s" s="2">
         <v>77</v>
@@ -10239,7 +10311,7 @@
         <v>76</v>
       </c>
       <c r="AJ73" t="s" s="2">
-        <v>139</v>
+        <v>142</v>
       </c>
       <c r="AK73" t="s" s="2">
         <v>76</v>
@@ -10248,7 +10320,7 @@
         <v>76</v>
       </c>
       <c r="AM73" t="s" s="2">
-        <v>178</v>
+        <v>186</v>
       </c>
       <c r="AN73" t="s" s="2">
         <v>76</v>
@@ -10256,14 +10328,14 @@
     </row>
     <row r="74" hidden="true">
       <c r="A74" t="s" s="2">
-        <v>441</v>
+        <v>456</v>
       </c>
       <c r="B74" t="s" s="2">
-        <v>441</v>
+        <v>456</v>
       </c>
       <c r="C74" s="2"/>
       <c r="D74" t="s" s="2">
-        <v>388</v>
+        <v>399</v>
       </c>
       <c r="E74" s="2"/>
       <c r="F74" t="s" s="2">
@@ -10285,16 +10357,16 @@
         <v>134</v>
       </c>
       <c r="L74" t="s" s="2">
-        <v>389</v>
+        <v>400</v>
       </c>
       <c r="M74" t="s" s="2">
-        <v>390</v>
+        <v>401</v>
       </c>
       <c r="N74" t="s" s="2">
         <v>137</v>
       </c>
       <c r="O74" t="s" s="2">
-        <v>143</v>
+        <v>146</v>
       </c>
       <c r="P74" t="s" s="2">
         <v>76</v>
@@ -10343,7 +10415,7 @@
         <v>76</v>
       </c>
       <c r="AF74" t="s" s="2">
-        <v>391</v>
+        <v>402</v>
       </c>
       <c r="AG74" t="s" s="2">
         <v>77</v>
@@ -10355,7 +10427,7 @@
         <v>76</v>
       </c>
       <c r="AJ74" t="s" s="2">
-        <v>139</v>
+        <v>142</v>
       </c>
       <c r="AK74" t="s" s="2">
         <v>76</v>
@@ -10372,10 +10444,10 @@
     </row>
     <row r="75" hidden="true">
       <c r="A75" t="s" s="2">
-        <v>442</v>
+        <v>457</v>
       </c>
       <c r="B75" t="s" s="2">
-        <v>442</v>
+        <v>457</v>
       </c>
       <c r="C75" s="2"/>
       <c r="D75" t="s" s="2">
@@ -10398,15 +10470,17 @@
         <v>76</v>
       </c>
       <c r="K75" t="s" s="2">
-        <v>167</v>
+        <v>172</v>
       </c>
       <c r="L75" t="s" s="2">
-        <v>443</v>
+        <v>458</v>
       </c>
       <c r="M75" t="s" s="2">
-        <v>444</v>
-      </c>
-      <c r="N75" s="2"/>
+        <v>459</v>
+      </c>
+      <c r="N75" t="s" s="2">
+        <v>175</v>
+      </c>
       <c r="O75" s="2"/>
       <c r="P75" t="s" s="2">
         <v>76</v>
@@ -10431,13 +10505,13 @@
         <v>76</v>
       </c>
       <c r="X75" t="s" s="2">
-        <v>170</v>
+        <v>176</v>
       </c>
       <c r="Y75" t="s" s="2">
-        <v>445</v>
+        <v>460</v>
       </c>
       <c r="Z75" t="s" s="2">
-        <v>446</v>
+        <v>461</v>
       </c>
       <c r="AA75" t="s" s="2">
         <v>76</v>
@@ -10455,7 +10529,7 @@
         <v>76</v>
       </c>
       <c r="AF75" t="s" s="2">
-        <v>442</v>
+        <v>457</v>
       </c>
       <c r="AG75" t="s" s="2">
         <v>88</v>
@@ -10464,7 +10538,7 @@
         <v>88</v>
       </c>
       <c r="AI75" t="s" s="2">
-        <v>76</v>
+        <v>154</v>
       </c>
       <c r="AJ75" t="s" s="2">
         <v>100</v>
@@ -10473,10 +10547,10 @@
         <v>76</v>
       </c>
       <c r="AL75" t="s" s="2">
-        <v>76</v>
+        <v>179</v>
       </c>
       <c r="AM75" t="s" s="2">
-        <v>76</v>
+        <v>180</v>
       </c>
       <c r="AN75" t="s" s="2">
         <v>76</v>
@@ -10484,10 +10558,10 @@
     </row>
     <row r="76" hidden="true">
       <c r="A76" t="s" s="2">
-        <v>447</v>
+        <v>462</v>
       </c>
       <c r="B76" t="s" s="2">
-        <v>447</v>
+        <v>462</v>
       </c>
       <c r="C76" s="2"/>
       <c r="D76" t="s" s="2">
@@ -10510,15 +10584,17 @@
         <v>76</v>
       </c>
       <c r="K76" t="s" s="2">
-        <v>448</v>
+        <v>463</v>
       </c>
       <c r="L76" t="s" s="2">
-        <v>449</v>
+        <v>464</v>
       </c>
       <c r="M76" t="s" s="2">
-        <v>450</v>
-      </c>
-      <c r="N76" s="2"/>
+        <v>465</v>
+      </c>
+      <c r="N76" t="s" s="2">
+        <v>384</v>
+      </c>
       <c r="O76" s="2"/>
       <c r="P76" t="s" s="2">
         <v>76</v>
@@ -10567,7 +10643,7 @@
         <v>76</v>
       </c>
       <c r="AF76" t="s" s="2">
-        <v>447</v>
+        <v>462</v>
       </c>
       <c r="AG76" t="s" s="2">
         <v>88</v>
@@ -10576,10 +10652,10 @@
         <v>88</v>
       </c>
       <c r="AI76" t="s" s="2">
-        <v>76</v>
+        <v>154</v>
       </c>
       <c r="AJ76" t="s" s="2">
-        <v>100</v>
+        <v>264</v>
       </c>
       <c r="AK76" t="s" s="2">
         <v>76</v>
@@ -10588,7 +10664,7 @@
         <v>76</v>
       </c>
       <c r="AM76" t="s" s="2">
-        <v>76</v>
+        <v>377</v>
       </c>
       <c r="AN76" t="s" s="2">
         <v>76</v>
@@ -10596,10 +10672,10 @@
     </row>
     <row r="77" hidden="true">
       <c r="A77" t="s" s="2">
-        <v>451</v>
+        <v>466</v>
       </c>
       <c r="B77" t="s" s="2">
-        <v>451</v>
+        <v>466</v>
       </c>
       <c r="C77" s="2"/>
       <c r="D77" t="s" s="2">
@@ -10622,23 +10698,23 @@
         <v>89</v>
       </c>
       <c r="K77" t="s" s="2">
-        <v>167</v>
+        <v>172</v>
       </c>
       <c r="L77" t="s" s="2">
-        <v>452</v>
+        <v>467</v>
       </c>
       <c r="M77" t="s" s="2">
-        <v>453</v>
+        <v>468</v>
       </c>
       <c r="N77" t="s" s="2">
-        <v>454</v>
+        <v>469</v>
       </c>
       <c r="O77" s="2"/>
       <c r="P77" t="s" s="2">
         <v>76</v>
       </c>
       <c r="Q77" t="s" s="2">
-        <v>455</v>
+        <v>470</v>
       </c>
       <c r="R77" t="s" s="2">
         <v>76</v>
@@ -10659,13 +10735,13 @@
         <v>76</v>
       </c>
       <c r="X77" t="s" s="2">
-        <v>456</v>
+        <v>471</v>
       </c>
       <c r="Y77" t="s" s="2">
-        <v>457</v>
+        <v>472</v>
       </c>
       <c r="Z77" t="s" s="2">
-        <v>458</v>
+        <v>473</v>
       </c>
       <c r="AA77" t="s" s="2">
         <v>76</v>
@@ -10683,7 +10759,7 @@
         <v>76</v>
       </c>
       <c r="AF77" t="s" s="2">
-        <v>451</v>
+        <v>466</v>
       </c>
       <c r="AG77" t="s" s="2">
         <v>77</v>
@@ -10692,7 +10768,7 @@
         <v>78</v>
       </c>
       <c r="AI77" t="s" s="2">
-        <v>76</v>
+        <v>154</v>
       </c>
       <c r="AJ77" t="s" s="2">
         <v>100</v>
@@ -10701,10 +10777,10 @@
         <v>76</v>
       </c>
       <c r="AL77" t="s" s="2">
-        <v>76</v>
+        <v>179</v>
       </c>
       <c r="AM77" t="s" s="2">
-        <v>76</v>
+        <v>180</v>
       </c>
       <c r="AN77" t="s" s="2">
         <v>76</v>
@@ -10712,10 +10788,10 @@
     </row>
     <row r="78" hidden="true">
       <c r="A78" t="s" s="2">
-        <v>459</v>
+        <v>474</v>
       </c>
       <c r="B78" t="s" s="2">
-        <v>459</v>
+        <v>474</v>
       </c>
       <c r="C78" s="2"/>
       <c r="D78" t="s" s="2">
@@ -10738,16 +10814,16 @@
         <v>89</v>
       </c>
       <c r="K78" t="s" s="2">
-        <v>186</v>
+        <v>191</v>
       </c>
       <c r="L78" t="s" s="2">
-        <v>460</v>
+        <v>475</v>
       </c>
       <c r="M78" t="s" s="2">
-        <v>461</v>
+        <v>476</v>
       </c>
       <c r="N78" t="s" s="2">
-        <v>462</v>
+        <v>477</v>
       </c>
       <c r="O78" s="2"/>
       <c r="P78" t="s" s="2">
@@ -10773,13 +10849,13 @@
         <v>76</v>
       </c>
       <c r="X78" t="s" s="2">
-        <v>170</v>
+        <v>176</v>
       </c>
       <c r="Y78" t="s" s="2">
-        <v>463</v>
+        <v>478</v>
       </c>
       <c r="Z78" t="s" s="2">
-        <v>464</v>
+        <v>479</v>
       </c>
       <c r="AA78" t="s" s="2">
         <v>76</v>
@@ -10797,7 +10873,7 @@
         <v>76</v>
       </c>
       <c r="AF78" t="s" s="2">
-        <v>459</v>
+        <v>474</v>
       </c>
       <c r="AG78" t="s" s="2">
         <v>77</v>
@@ -10806,7 +10882,7 @@
         <v>78</v>
       </c>
       <c r="AI78" t="s" s="2">
-        <v>76</v>
+        <v>154</v>
       </c>
       <c r="AJ78" t="s" s="2">
         <v>100</v>
@@ -10815,10 +10891,10 @@
         <v>76</v>
       </c>
       <c r="AL78" t="s" s="2">
-        <v>76</v>
+        <v>480</v>
       </c>
       <c r="AM78" t="s" s="2">
-        <v>76</v>
+        <v>481</v>
       </c>
       <c r="AN78" t="s" s="2">
         <v>76</v>
@@ -10826,10 +10902,10 @@
     </row>
     <row r="79" hidden="true">
       <c r="A79" t="s" s="2">
-        <v>465</v>
+        <v>482</v>
       </c>
       <c r="B79" t="s" s="2">
-        <v>465</v>
+        <v>482</v>
       </c>
       <c r="C79" s="2"/>
       <c r="D79" t="s" s="2">
@@ -10852,16 +10928,16 @@
         <v>89</v>
       </c>
       <c r="K79" t="s" s="2">
-        <v>186</v>
+        <v>191</v>
       </c>
       <c r="L79" t="s" s="2">
-        <v>466</v>
+        <v>483</v>
       </c>
       <c r="M79" t="s" s="2">
-        <v>467</v>
+        <v>484</v>
       </c>
       <c r="N79" t="s" s="2">
-        <v>468</v>
+        <v>485</v>
       </c>
       <c r="O79" s="2"/>
       <c r="P79" t="s" s="2">
@@ -10887,13 +10963,13 @@
         <v>76</v>
       </c>
       <c r="X79" t="s" s="2">
-        <v>170</v>
+        <v>176</v>
       </c>
       <c r="Y79" t="s" s="2">
-        <v>469</v>
+        <v>486</v>
       </c>
       <c r="Z79" t="s" s="2">
-        <v>470</v>
+        <v>487</v>
       </c>
       <c r="AA79" t="s" s="2">
         <v>76</v>
@@ -10911,7 +10987,7 @@
         <v>76</v>
       </c>
       <c r="AF79" t="s" s="2">
-        <v>465</v>
+        <v>482</v>
       </c>
       <c r="AG79" t="s" s="2">
         <v>77</v>
@@ -10920,7 +10996,7 @@
         <v>78</v>
       </c>
       <c r="AI79" t="s" s="2">
-        <v>76</v>
+        <v>154</v>
       </c>
       <c r="AJ79" t="s" s="2">
         <v>100</v>
@@ -10929,10 +11005,10 @@
         <v>76</v>
       </c>
       <c r="AL79" t="s" s="2">
-        <v>76</v>
+        <v>480</v>
       </c>
       <c r="AM79" t="s" s="2">
-        <v>76</v>
+        <v>481</v>
       </c>
       <c r="AN79" t="s" s="2">
         <v>76</v>
@@ -10940,10 +11016,10 @@
     </row>
     <row r="80" hidden="true">
       <c r="A80" t="s" s="2">
-        <v>471</v>
+        <v>488</v>
       </c>
       <c r="B80" t="s" s="2">
-        <v>471</v>
+        <v>488</v>
       </c>
       <c r="C80" s="2"/>
       <c r="D80" t="s" s="2">
@@ -10966,16 +11042,16 @@
         <v>89</v>
       </c>
       <c r="K80" t="s" s="2">
-        <v>186</v>
+        <v>191</v>
       </c>
       <c r="L80" t="s" s="2">
-        <v>472</v>
+        <v>489</v>
       </c>
       <c r="M80" t="s" s="2">
-        <v>473</v>
+        <v>490</v>
       </c>
       <c r="N80" t="s" s="2">
-        <v>474</v>
+        <v>491</v>
       </c>
       <c r="O80" s="2"/>
       <c r="P80" t="s" s="2">
@@ -11001,13 +11077,13 @@
         <v>76</v>
       </c>
       <c r="X80" t="s" s="2">
-        <v>170</v>
+        <v>176</v>
       </c>
       <c r="Y80" t="s" s="2">
-        <v>475</v>
+        <v>492</v>
       </c>
       <c r="Z80" t="s" s="2">
-        <v>476</v>
+        <v>493</v>
       </c>
       <c r="AA80" t="s" s="2">
         <v>76</v>
@@ -11025,7 +11101,7 @@
         <v>76</v>
       </c>
       <c r="AF80" t="s" s="2">
-        <v>471</v>
+        <v>488</v>
       </c>
       <c r="AG80" t="s" s="2">
         <v>77</v>
@@ -11034,7 +11110,7 @@
         <v>78</v>
       </c>
       <c r="AI80" t="s" s="2">
-        <v>76</v>
+        <v>154</v>
       </c>
       <c r="AJ80" t="s" s="2">
         <v>100</v>
@@ -11043,10 +11119,10 @@
         <v>76</v>
       </c>
       <c r="AL80" t="s" s="2">
-        <v>76</v>
+        <v>480</v>
       </c>
       <c r="AM80" t="s" s="2">
-        <v>76</v>
+        <v>481</v>
       </c>
       <c r="AN80" t="s" s="2">
         <v>76</v>
@@ -11054,10 +11130,10 @@
     </row>
     <row r="81" hidden="true">
       <c r="A81" t="s" s="2">
-        <v>477</v>
+        <v>494</v>
       </c>
       <c r="B81" t="s" s="2">
-        <v>477</v>
+        <v>494</v>
       </c>
       <c r="C81" s="2"/>
       <c r="D81" t="s" s="2">
@@ -11080,16 +11156,16 @@
         <v>89</v>
       </c>
       <c r="K81" t="s" s="2">
-        <v>167</v>
+        <v>172</v>
       </c>
       <c r="L81" t="s" s="2">
-        <v>478</v>
+        <v>495</v>
       </c>
       <c r="M81" t="s" s="2">
-        <v>479</v>
+        <v>496</v>
       </c>
       <c r="N81" t="s" s="2">
-        <v>480</v>
+        <v>497</v>
       </c>
       <c r="O81" s="2"/>
       <c r="P81" t="s" s="2">
@@ -11115,13 +11191,13 @@
         <v>76</v>
       </c>
       <c r="X81" t="s" s="2">
-        <v>456</v>
+        <v>471</v>
       </c>
       <c r="Y81" t="s" s="2">
-        <v>481</v>
+        <v>498</v>
       </c>
       <c r="Z81" t="s" s="2">
-        <v>482</v>
+        <v>499</v>
       </c>
       <c r="AA81" t="s" s="2">
         <v>76</v>
@@ -11139,7 +11215,7 @@
         <v>76</v>
       </c>
       <c r="AF81" t="s" s="2">
-        <v>477</v>
+        <v>494</v>
       </c>
       <c r="AG81" t="s" s="2">
         <v>77</v>
@@ -11148,7 +11224,7 @@
         <v>78</v>
       </c>
       <c r="AI81" t="s" s="2">
-        <v>76</v>
+        <v>154</v>
       </c>
       <c r="AJ81" t="s" s="2">
         <v>100</v>
@@ -11157,10 +11233,10 @@
         <v>76</v>
       </c>
       <c r="AL81" t="s" s="2">
-        <v>76</v>
+        <v>179</v>
       </c>
       <c r="AM81" t="s" s="2">
-        <v>76</v>
+        <v>180</v>
       </c>
       <c r="AN81" t="s" s="2">
         <v>76</v>
@@ -11168,10 +11244,10 @@
     </row>
     <row r="82" hidden="true">
       <c r="A82" t="s" s="2">
-        <v>483</v>
+        <v>500</v>
       </c>
       <c r="B82" t="s" s="2">
-        <v>483</v>
+        <v>500</v>
       </c>
       <c r="C82" s="2"/>
       <c r="D82" t="s" s="2">
@@ -11194,16 +11270,16 @@
         <v>89</v>
       </c>
       <c r="K82" t="s" s="2">
-        <v>325</v>
+        <v>332</v>
       </c>
       <c r="L82" t="s" s="2">
-        <v>484</v>
+        <v>501</v>
       </c>
       <c r="M82" t="s" s="2">
-        <v>485</v>
+        <v>502</v>
       </c>
       <c r="N82" t="s" s="2">
-        <v>486</v>
+        <v>503</v>
       </c>
       <c r="O82" s="2"/>
       <c r="P82" t="s" s="2">
@@ -11253,7 +11329,7 @@
         <v>76</v>
       </c>
       <c r="AF82" t="s" s="2">
-        <v>483</v>
+        <v>500</v>
       </c>
       <c r="AG82" t="s" s="2">
         <v>77</v>
@@ -11262,19 +11338,19 @@
         <v>88</v>
       </c>
       <c r="AI82" t="s" s="2">
-        <v>76</v>
+        <v>154</v>
       </c>
       <c r="AJ82" t="s" s="2">
-        <v>100</v>
+        <v>337</v>
       </c>
       <c r="AK82" t="s" s="2">
         <v>76</v>
       </c>
       <c r="AL82" t="s" s="2">
-        <v>76</v>
+        <v>448</v>
       </c>
       <c r="AM82" t="s" s="2">
-        <v>76</v>
+        <v>449</v>
       </c>
       <c r="AN82" t="s" s="2">
         <v>76</v>
@@ -11282,10 +11358,10 @@
     </row>
     <row r="83" hidden="true">
       <c r="A83" t="s" s="2">
-        <v>487</v>
+        <v>504</v>
       </c>
       <c r="B83" t="s" s="2">
-        <v>487</v>
+        <v>504</v>
       </c>
       <c r="C83" s="2"/>
       <c r="D83" t="s" s="2">
@@ -11308,13 +11384,13 @@
         <v>89</v>
       </c>
       <c r="K83" t="s" s="2">
-        <v>382</v>
+        <v>393</v>
       </c>
       <c r="L83" t="s" s="2">
-        <v>488</v>
+        <v>505</v>
       </c>
       <c r="M83" t="s" s="2">
-        <v>489</v>
+        <v>506</v>
       </c>
       <c r="N83" s="2"/>
       <c r="O83" s="2"/>
@@ -11322,7 +11398,7 @@
         <v>76</v>
       </c>
       <c r="Q83" t="s" s="2">
-        <v>490</v>
+        <v>507</v>
       </c>
       <c r="R83" t="s" s="2">
         <v>76</v>
@@ -11367,7 +11443,7 @@
         <v>76</v>
       </c>
       <c r="AF83" t="s" s="2">
-        <v>487</v>
+        <v>504</v>
       </c>
       <c r="AG83" t="s" s="2">
         <v>77</v>
@@ -11376,7 +11452,7 @@
         <v>78</v>
       </c>
       <c r="AI83" t="s" s="2">
-        <v>76</v>
+        <v>154</v>
       </c>
       <c r="AJ83" t="s" s="2">
         <v>100</v>
@@ -11388,7 +11464,7 @@
         <v>76</v>
       </c>
       <c r="AM83" t="s" s="2">
-        <v>259</v>
+        <v>266</v>
       </c>
       <c r="AN83" t="s" s="2">
         <v>76</v>
@@ -11396,10 +11472,10 @@
     </row>
     <row r="84" hidden="true">
       <c r="A84" t="s" s="2">
-        <v>491</v>
+        <v>508</v>
       </c>
       <c r="B84" t="s" s="2">
-        <v>491</v>
+        <v>508</v>
       </c>
       <c r="C84" s="2"/>
       <c r="D84" t="s" s="2">
@@ -11422,13 +11498,13 @@
         <v>76</v>
       </c>
       <c r="K84" t="s" s="2">
-        <v>174</v>
+        <v>182</v>
       </c>
       <c r="L84" t="s" s="2">
-        <v>175</v>
+        <v>183</v>
       </c>
       <c r="M84" t="s" s="2">
-        <v>176</v>
+        <v>184</v>
       </c>
       <c r="N84" s="2"/>
       <c r="O84" s="2"/>
@@ -11479,7 +11555,7 @@
         <v>76</v>
       </c>
       <c r="AF84" t="s" s="2">
-        <v>177</v>
+        <v>185</v>
       </c>
       <c r="AG84" t="s" s="2">
         <v>77</v>
@@ -11500,7 +11576,7 @@
         <v>76</v>
       </c>
       <c r="AM84" t="s" s="2">
-        <v>178</v>
+        <v>186</v>
       </c>
       <c r="AN84" t="s" s="2">
         <v>76</v>
@@ -11508,10 +11584,10 @@
     </row>
     <row r="85" hidden="true">
       <c r="A85" t="s" s="2">
-        <v>492</v>
+        <v>509</v>
       </c>
       <c r="B85" t="s" s="2">
-        <v>492</v>
+        <v>509</v>
       </c>
       <c r="C85" s="2"/>
       <c r="D85" t="s" s="2">
@@ -11540,7 +11616,7 @@
         <v>135</v>
       </c>
       <c r="M85" t="s" s="2">
-        <v>180</v>
+        <v>188</v>
       </c>
       <c r="N85" t="s" s="2">
         <v>137</v>
@@ -11581,19 +11657,19 @@
         <v>76</v>
       </c>
       <c r="AB85" t="s" s="2">
-        <v>76</v>
+        <v>138</v>
       </c>
       <c r="AC85" t="s" s="2">
-        <v>76</v>
+        <v>139</v>
       </c>
       <c r="AD85" t="s" s="2">
         <v>76</v>
       </c>
       <c r="AE85" t="s" s="2">
-        <v>76</v>
+        <v>140</v>
       </c>
       <c r="AF85" t="s" s="2">
-        <v>184</v>
+        <v>189</v>
       </c>
       <c r="AG85" t="s" s="2">
         <v>77</v>
@@ -11605,7 +11681,7 @@
         <v>76</v>
       </c>
       <c r="AJ85" t="s" s="2">
-        <v>139</v>
+        <v>142</v>
       </c>
       <c r="AK85" t="s" s="2">
         <v>76</v>
@@ -11614,7 +11690,7 @@
         <v>76</v>
       </c>
       <c r="AM85" t="s" s="2">
-        <v>178</v>
+        <v>186</v>
       </c>
       <c r="AN85" t="s" s="2">
         <v>76</v>
@@ -11622,14 +11698,14 @@
     </row>
     <row r="86" hidden="true">
       <c r="A86" t="s" s="2">
-        <v>493</v>
+        <v>510</v>
       </c>
       <c r="B86" t="s" s="2">
-        <v>493</v>
+        <v>510</v>
       </c>
       <c r="C86" s="2"/>
       <c r="D86" t="s" s="2">
-        <v>388</v>
+        <v>399</v>
       </c>
       <c r="E86" s="2"/>
       <c r="F86" t="s" s="2">
@@ -11651,16 +11727,16 @@
         <v>134</v>
       </c>
       <c r="L86" t="s" s="2">
-        <v>389</v>
+        <v>400</v>
       </c>
       <c r="M86" t="s" s="2">
-        <v>390</v>
+        <v>401</v>
       </c>
       <c r="N86" t="s" s="2">
         <v>137</v>
       </c>
       <c r="O86" t="s" s="2">
-        <v>143</v>
+        <v>146</v>
       </c>
       <c r="P86" t="s" s="2">
         <v>76</v>
@@ -11709,7 +11785,7 @@
         <v>76</v>
       </c>
       <c r="AF86" t="s" s="2">
-        <v>391</v>
+        <v>402</v>
       </c>
       <c r="AG86" t="s" s="2">
         <v>77</v>
@@ -11721,7 +11797,7 @@
         <v>76</v>
       </c>
       <c r="AJ86" t="s" s="2">
-        <v>139</v>
+        <v>142</v>
       </c>
       <c r="AK86" t="s" s="2">
         <v>76</v>
@@ -11738,10 +11814,10 @@
     </row>
     <row r="87" hidden="true">
       <c r="A87" t="s" s="2">
-        <v>494</v>
+        <v>511</v>
       </c>
       <c r="B87" t="s" s="2">
-        <v>494</v>
+        <v>511</v>
       </c>
       <c r="C87" s="2"/>
       <c r="D87" t="s" s="2">
@@ -11767,10 +11843,10 @@
         <v>108</v>
       </c>
       <c r="L87" t="s" s="2">
-        <v>495</v>
+        <v>512</v>
       </c>
       <c r="M87" t="s" s="2">
-        <v>496</v>
+        <v>513</v>
       </c>
       <c r="N87" s="2"/>
       <c r="O87" s="2"/>
@@ -11797,13 +11873,13 @@
         <v>76</v>
       </c>
       <c r="X87" t="s" s="2">
-        <v>159</v>
+        <v>164</v>
       </c>
       <c r="Y87" t="s" s="2">
-        <v>497</v>
+        <v>514</v>
       </c>
       <c r="Z87" t="s" s="2">
-        <v>498</v>
+        <v>515</v>
       </c>
       <c r="AA87" t="s" s="2">
         <v>76</v>
@@ -11821,7 +11897,7 @@
         <v>76</v>
       </c>
       <c r="AF87" t="s" s="2">
-        <v>494</v>
+        <v>511</v>
       </c>
       <c r="AG87" t="s" s="2">
         <v>88</v>
@@ -11850,10 +11926,10 @@
     </row>
     <row r="88" hidden="true">
       <c r="A88" t="s" s="2">
-        <v>499</v>
+        <v>516</v>
       </c>
       <c r="B88" t="s" s="2">
-        <v>499</v>
+        <v>516</v>
       </c>
       <c r="C88" s="2"/>
       <c r="D88" t="s" s="2">
@@ -11876,15 +11952,17 @@
         <v>89</v>
       </c>
       <c r="K88" t="s" s="2">
-        <v>500</v>
+        <v>517</v>
       </c>
       <c r="L88" t="s" s="2">
-        <v>501</v>
+        <v>518</v>
       </c>
       <c r="M88" t="s" s="2">
-        <v>502</v>
-      </c>
-      <c r="N88" s="2"/>
+        <v>519</v>
+      </c>
+      <c r="N88" t="s" s="2">
+        <v>384</v>
+      </c>
       <c r="O88" s="2"/>
       <c r="P88" t="s" s="2">
         <v>76</v>
@@ -11933,7 +12011,7 @@
         <v>76</v>
       </c>
       <c r="AF88" t="s" s="2">
-        <v>499</v>
+        <v>516</v>
       </c>
       <c r="AG88" t="s" s="2">
         <v>88</v>
@@ -11942,10 +12020,10 @@
         <v>88</v>
       </c>
       <c r="AI88" t="s" s="2">
-        <v>76</v>
+        <v>154</v>
       </c>
       <c r="AJ88" t="s" s="2">
-        <v>100</v>
+        <v>264</v>
       </c>
       <c r="AK88" t="s" s="2">
         <v>76</v>
@@ -11954,7 +12032,7 @@
         <v>76</v>
       </c>
       <c r="AM88" t="s" s="2">
-        <v>76</v>
+        <v>377</v>
       </c>
       <c r="AN88" t="s" s="2">
         <v>76</v>
@@ -11962,10 +12040,10 @@
     </row>
     <row r="89" hidden="true">
       <c r="A89" t="s" s="2">
-        <v>503</v>
+        <v>520</v>
       </c>
       <c r="B89" t="s" s="2">
-        <v>503</v>
+        <v>520</v>
       </c>
       <c r="C89" s="2"/>
       <c r="D89" t="s" s="2">
@@ -11991,10 +12069,10 @@
         <v>79</v>
       </c>
       <c r="L89" t="s" s="2">
-        <v>504</v>
+        <v>521</v>
       </c>
       <c r="M89" t="s" s="2">
-        <v>505</v>
+        <v>522</v>
       </c>
       <c r="N89" s="2"/>
       <c r="O89" s="2"/>
@@ -12045,7 +12123,7 @@
         <v>76</v>
       </c>
       <c r="AF89" t="s" s="2">
-        <v>503</v>
+        <v>520</v>
       </c>
       <c r="AG89" t="s" s="2">
         <v>77</v>
@@ -12057,7 +12135,7 @@
         <v>76</v>
       </c>
       <c r="AJ89" t="s" s="2">
-        <v>100</v>
+        <v>76</v>
       </c>
       <c r="AK89" t="s" s="2">
         <v>76</v>
